--- a/outputs/chain-update-20261028/bfresh.xlsx
+++ b/outputs/chain-update-20261028/bfresh.xlsx
@@ -34,13 +34,13 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'שער'!$A1:$F13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'מקרא והנחיות'!$A1:$F35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'פירוק והריסה'!$A1:$F12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'מחיצות והכנות לדלפק'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'מחיצות והכנות לדלפק'!$A1:$F11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'אינסטלציה ותברואה'!$A1:$F12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'חשמל והכנות תקשורת'!$A1:$F15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'חשמל והכנות תקשורת'!$A1:$F20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'הכנות רצפה והגבהות'!$A1:$F7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'איטום'!$A1:$F7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'דלתות בחנות או בחדר שירות'!$A1:$F7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'ריצוף וחיפוי הדלפק'!$A1:$F11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'ריצוף וחיפוי הדלפק'!$A1:$F12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'תקרה וקרניזים לדוכן'!$A1:$F8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'צבע וגמר'!$A1:$F8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'נגרות ביפרש'!$A1:$F11</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="416">
   <si>
     <t>פירוט טכני וכתב כמויות</t>
   </si>
@@ -165,7 +165,7 @@
     <t>2. אספקה, התקנה, תשתית וחיבור בידי קבלנים או ספקים שונים יפורטו בנפרד. אין להסיק אחריות רק מהופעת שם ספק או מהסימון קיים.</t>
   </si>
   <si>
-    <t>3. מפרטי הרשת שנקבעו בשורות נשמרים. רק פרטי סניף ובחירות שנותרו פתוחות יושלמו לפי מסמכי הפרויקט וההכרעות המאושרים; אין למלא מחלוקת מערך של סניף קודם ללא אישור.</t>
+    <t>3. מפרטי הרשת שנקבעו בשורות נשמרים. רק פרטי סניף ובחירות שנותרו פתוחות יושלמו לפי מסמכי הפרויקט וההכרעות המאושרים.</t>
   </si>
   <si>
     <t>4. לכל רכיב תכולת תמחור אחת. אספקה או עבודה המופיעות בפרק נפרד יוחרגו ממחיר הפריט שבו היו עלולות להיכלל שוב.</t>
@@ -180,16 +180,16 @@
     <t>contractor</t>
   </si>
   <si>
-    <t>d6d6b0e3-35ba-4a70-b25a-644b4fcb2752</t>
-  </si>
-  <si>
-    <t>9164786e-25f1-4590-bd1c-10b21b694cb9</t>
+    <t>fcf94e11-c9fe-4658-ab67-b9ba269e9b8b</t>
+  </si>
+  <si>
+    <t>0716dc2b-adaa-4555-81be-fd06ccd145ea</t>
   </si>
   <si>
     <t>bfresh</t>
   </si>
   <si>
-    <t>["8189bc4f-d508-4fbf-af8e-947594637817","e7f7d9dd-858f-45b5-85a3-26465f8d29d1","c8c2cbd0-6b00-4f97-9970-14224685d7a0","3716ff48-6609-494b-8182-59ff37209cf5","0877b93e-6c74-451a-84c3-1890085b89fb","859f33f1-9a45-4c6a-aeb9-53d787cbffff","004b11c9-e9fe-4bc9-a628-b25d45f52687","f168410b-fdac-47e6-a2c9-cb836f8a21b7","8ca27162-cf4c-4235-9625-144bc5f8b3b8","e11d6aeb-dad6-48da-a2ff-73af4a3884cb","78f2831d-b2fe-4cc4-8a44-bf741ea81b7f","1c6df516-1715-4ad1-8bcd-2f628170a9ab","0e5a14aa-9bf4-4548-9938-f5cfffa73598","7530b13f-fabb-41fe-9523-01f3cac97750","4d50a42d-8662-461f-a783-aee52c2ab469","044361b7-a153-40d6-9552-4292637bb427","cb524d1f-62a7-4303-acfe-7f207f94b8d6","eaf4a6ee-6dd6-4504-87ec-302f84ef4b45","422ba6c0-3a4d-491c-b266-dae2195b3cce","63ea7e18-6a0d-4990-8cdb-03d40038c15c","5d74e8dc-9ffe-438f-844c-d5b9d72d6154"]</t>
+    <t>["4938ad8e-30f6-4db3-b36e-88bd5f31371a","a2f388ba-4d82-4f6f-9957-1ece9d40a5b3","36015ada-bf8b-4d3f-ae03-b9b57aa7b873","e3f2cb89-0c46-4991-ab5a-e328886fafc9","d557a98c-fbaa-46a2-9e27-97ce871d7cf8","981a101b-caae-43c7-a83a-c31e0151c58a","47355eee-c567-4b20-aedc-90e5e05bc6fb","d379600b-3f53-456b-a981-4e9abc8f5997","fa923af1-2e11-497f-823e-b095102a0738","62d1df6b-4aec-4086-a7ab-09b4118c9ae3","edcd958a-696f-4474-a659-5827bc5a06c9","bb309645-3770-4ee9-8b2c-0e85d55b52ad","48a88d49-120d-4f44-b6ed-066bf3630c9e","82ccff6c-0b84-4da2-9ea5-dcaffd1c18a1","bc014ef7-3a7c-4d06-a3eb-da40c6c45434","a5d4682d-1a3a-49cf-8468-2fa8dbcc9807","8af97b24-cd36-4ca2-9464-df9ba4c55038","232c2361-9c27-484e-add5-86dbd53b8d8b","b3c2a399-0722-446d-a339-110b8f4a3f8c","46b8609d-784d-4611-a563-4896ff0be7d0","b7870e32-b79e-4c5a-990d-790a5fd939d8"]</t>
   </si>
   <si>
     <t>layout</t>
@@ -216,130 +216,130 @@
     <t>rowIds</t>
   </si>
   <si>
-    <t>8189bc4f-d508-4fbf-af8e-947594637817</t>
-  </si>
-  <si>
-    <t>["1b2325c4-3966-498f-8366-a0f5dda84597","0bfab241-ed81-43ee-99b0-5526452543a7","b4a6859b-aadb-4a39-859d-136a349ec68c","5a048a3b-1e97-41e1-bbaf-f07b3e5a1af8","4bc42c11-c26d-4db2-9bed-59b566c56110","81b27a8b-b6cf-406b-9a4f-4064fd0e67ce","e3f473bc-d7e6-46b1-984d-3181e8d54797","070e4db8-dea0-48c6-956d-0c3a3be755b0"]</t>
-  </si>
-  <si>
-    <t>e7f7d9dd-858f-45b5-85a3-26465f8d29d1</t>
-  </si>
-  <si>
-    <t>["89ec1321-ba79-4713-9bd0-0c59184ce03f","e2a1ca32-0e8e-4f85-9128-d045e82423f9","510a2791-66f0-499a-b814-91c4e57deb43","0a23b5af-82e5-46aa-bef6-7362e7c40c87","06cac1d3-0240-43e5-ab54-96c72adc3ca0","f97b0dae-366b-48bf-9519-7bc170cb2766"]</t>
-  </si>
-  <si>
-    <t>c8c2cbd0-6b00-4f97-9970-14224685d7a0</t>
-  </si>
-  <si>
-    <t>["092f557e-3e6d-4dac-980b-fd4f0c61f9c7","2811b5de-0b50-4acf-acb4-3b5c53525d1f","0cde9a76-fa91-402d-8488-94c9c574b974","09dbb842-7103-4270-97e3-fc858f2b9bfa","d85e0b12-5b80-4b4b-81e6-4447766dd4e7","f9e4c395-0fcd-4cf5-8a14-9db72695105f","8353bc9d-b942-445e-80a8-787dea0c752e","0d5e5a43-8ea4-4402-99e7-ea8f9b6a714f"]</t>
-  </si>
-  <si>
-    <t>3716ff48-6609-494b-8182-59ff37209cf5</t>
-  </si>
-  <si>
-    <t>["a5538cd3-1abd-44d5-858e-058a8ab6b72d","1b5296c6-de36-4329-b2e5-25d47b534a89","73197d04-2d4d-4608-a0ca-03c64087c7f9","7697e26b-4e56-407f-85a7-279bb9abcaef","3098007d-3d51-4129-815b-8e2d0a8a9fc9","69f96b77-f6b6-4c7d-ad66-ecbca9ded3e3","1cd83078-58d3-4fa8-8e49-45b89032bcbf","b8e01dec-be46-41c0-8713-a61f281f92fd","9b4db498-670d-4e7c-b392-976f68575547","b42e0cb8-4764-4c95-9206-a702a3ca94fa","880cc642-297a-42d8-b61f-31afc044a081"]</t>
-  </si>
-  <si>
-    <t>0877b93e-6c74-451a-84c3-1890085b89fb</t>
-  </si>
-  <si>
-    <t>["8eb99a66-c8da-4a85-a2e8-263b4882b200","bf62f5ce-1eac-4520-b186-93108dfcdd4e"]</t>
-  </si>
-  <si>
-    <t>859f33f1-9a45-4c6a-aeb9-53d787cbffff</t>
-  </si>
-  <si>
-    <t>["c29540f3-d119-4395-bc60-4274c439e0e2","3df8333e-a3b0-4391-9a1e-b3d44e5439aa"]</t>
-  </si>
-  <si>
-    <t>004b11c9-e9fe-4bc9-a628-b25d45f52687</t>
-  </si>
-  <si>
-    <t>["59988ad9-fe8c-426c-b71f-00890db727f8","da179852-7c12-45bc-bd39-523c09d68224"]</t>
-  </si>
-  <si>
-    <t>f168410b-fdac-47e6-a2c9-cb836f8a21b7</t>
-  </si>
-  <si>
-    <t>["2706522f-38a0-44a0-8be9-f9afa33c4b6e","f88046c6-21f1-4ac8-b189-b2dafa348bf3","8529bf7c-eaf0-4510-b50c-306442581bce","64b035af-4601-4388-93ca-c94bc58dff83","cd04e3f9-8ca9-4f41-a059-6e5c1b8b115f","b0c8b859-961f-4ae0-8753-f22a36c4b5ed","b36f8fc7-83c3-4bbd-9c96-8427d842fcd9"]</t>
-  </si>
-  <si>
-    <t>8ca27162-cf4c-4235-9625-144bc5f8b3b8</t>
-  </si>
-  <si>
-    <t>["c5d5a26a-cdf1-414b-99d6-4f6d5a6037df","791d629c-829a-4192-af58-0003592fb5d4","d7028dfd-f9c5-47fc-9546-314b8c314e0b"]</t>
-  </si>
-  <si>
-    <t>e11d6aeb-dad6-48da-a2ff-73af4a3884cb</t>
-  </si>
-  <si>
-    <t>["933649d2-61ca-4673-9bd0-9bf2dda9ad08","ba766927-4f03-4179-92d8-6c6e51f354b3","df5a3fb5-c708-48a4-b3fb-4eeb6877449f","02ac2483-3766-4e87-9642-a7538fa09b5e"]</t>
-  </si>
-  <si>
-    <t>78f2831d-b2fe-4cc4-8a44-bf741ea81b7f</t>
-  </si>
-  <si>
-    <t>["77077759-eca1-4237-b460-2fedc4e61575","5e73d0f2-1aab-4b35-9404-644e8e8734ab","adb34e5f-abfc-49e2-9d76-19db9e87e7d4","870e4611-5e0d-4302-b0d6-c9129b6ab79d","f4c2e9cd-a657-4712-810c-af158ce59e1a","b8f78421-12e0-4c9a-a585-05d1131e0c5d","9e0af212-d35f-4346-bd50-afbe618ec86a"]</t>
-  </si>
-  <si>
-    <t>1c6df516-1715-4ad1-8bcd-2f628170a9ab</t>
-  </si>
-  <si>
-    <t>["43534dfe-d369-429c-b2f9-469d130c9b7e","a4701464-123d-44f4-9e1a-a2d784fb3481","8176c706-3602-4bd6-93e6-7e85344bb0fe","d30dc058-e754-42aa-930d-fdf9936518c9","240649a4-986b-4ea3-91f7-bb92df91dfd1","4087d0f4-41bf-46d9-92cb-1a32f43550c4","e062b74d-4237-47e0-a444-785c70dd1ce0","cb910325-b9f3-453d-b7e0-9cf6dfb5954f","bc375460-a6ad-443b-9283-39151afa9d58"]</t>
-  </si>
-  <si>
-    <t>0e5a14aa-9bf4-4548-9938-f5cfffa73598</t>
-  </si>
-  <si>
-    <t>["c2ddd13f-b748-4789-bcfb-fc799a945e39","0758be5f-dc5e-49e8-82f8-e9f756071631","d5a0f1f9-7ef0-4b71-a688-57ad080ad214","862377fd-42e5-4b4c-b6d1-f8abddcc938e","1bcf48e6-a29b-4913-83b9-671bd262ab26"]</t>
-  </si>
-  <si>
-    <t>7530b13f-fabb-41fe-9523-01f3cac97750</t>
-  </si>
-  <si>
-    <t>["b2b4daf5-d986-428a-b4e5-096166af4a0a","708ecb63-c3dc-40a7-a346-a91f5ad2bdf3","c134bfb7-939b-496a-9e70-8a6a7a3d96c5","57282de5-e5a7-48d0-93db-d093957675c1","aa3618dd-746f-4f87-affc-2f103d6e3fe9","f73fa722-1ea6-4368-ad3b-c095740b75da"]</t>
-  </si>
-  <si>
-    <t>4d50a42d-8662-461f-a783-aee52c2ab469</t>
-  </si>
-  <si>
-    <t>["5ea8ad7f-0828-41b3-8b09-d4e8b0f57a07","400177af-7fe0-43eb-a111-588c4f445c3c","46d13d85-a281-4238-ada6-b1d8c670556c","50741612-b365-4216-8cd4-e3c8884dd716"]</t>
-  </si>
-  <si>
-    <t>044361b7-a153-40d6-9552-4292637bb427</t>
-  </si>
-  <si>
-    <t>["e89605ed-c940-4327-bd98-9501b7725240","eb037280-056d-42ef-a362-1f0023849d3e"]</t>
-  </si>
-  <si>
-    <t>cb524d1f-62a7-4303-acfe-7f207f94b8d6</t>
-  </si>
-  <si>
-    <t>["8b3c1c07-f9b4-4244-ac0a-e02bcb47a252","43ed42ac-04e6-42ed-bcfb-ba2ea0937ba3"]</t>
-  </si>
-  <si>
-    <t>eaf4a6ee-6dd6-4504-87ec-302f84ef4b45</t>
-  </si>
-  <si>
-    <t>["bd0cb7cf-2954-4926-8dd0-9e6dd447fb29","11c1874d-e02a-4d99-bae8-6e1f6ed480bb"]</t>
-  </si>
-  <si>
-    <t>422ba6c0-3a4d-491c-b266-dae2195b3cce</t>
-  </si>
-  <si>
-    <t>["081bd666-a85d-432b-a361-7d4d2a7a0724","7582ad5a-817c-4a6e-89fa-aed0e5d540f5","2c1bc97f-7c6f-4322-bd74-8d582df9ab9d"]</t>
-  </si>
-  <si>
-    <t>63ea7e18-6a0d-4990-8cdb-03d40038c15c</t>
-  </si>
-  <si>
-    <t>["85d398ac-d801-45b6-ad38-25eaa60363a8","b419cbf9-e1c1-4cbb-b922-551bda1c93e2"]</t>
-  </si>
-  <si>
-    <t>5d74e8dc-9ffe-438f-844c-d5b9d72d6154</t>
-  </si>
-  <si>
-    <t>["9d72ad11-d181-4a95-8f42-8f46cb7a5c8d","efa2d487-7bff-4c57-9999-f2892375b0fe"]</t>
+    <t>4938ad8e-30f6-4db3-b36e-88bd5f31371a</t>
+  </si>
+  <si>
+    <t>["973d9ae9-4cec-4f7d-8439-e1ccf2352869","2b24a6d4-7f01-4833-ac95-5620fb5f9d4d","7963bb1d-2a2d-4492-a854-625e02ed7ae6","dd177ffd-cd7a-48ed-bcec-55f4a1d5da18","634ff637-2288-4579-99e2-a7b3add4f18c","23dbaac1-360b-44be-84d2-46bbc399a5ea","f81b49d2-e7a4-4f3f-8d58-71d9297f4464","081d1ca5-39e7-4c93-9e84-f31e487fde6e"]</t>
+  </si>
+  <si>
+    <t>a2f388ba-4d82-4f6f-9957-1ece9d40a5b3</t>
+  </si>
+  <si>
+    <t>["256d7b19-ad40-4c88-8eeb-59612a2b500e","39bd191e-d21e-4494-b9d1-1c8d48bf0b6f","532c0665-7ca7-49c5-bc97-18a2433bcb8b","3df0dcbc-66c2-413b-8dbe-692aa4b14962","af949811-1c6f-4be8-9d86-426aa29f7171","e7105ff8-e123-4fe0-99c3-440293f1f930","c7cc79c7-fe11-435e-b562-a1cae8d0a0a0"]</t>
+  </si>
+  <si>
+    <t>36015ada-bf8b-4d3f-ae03-b9b57aa7b873</t>
+  </si>
+  <si>
+    <t>["155a6b9e-2d80-4526-8ed5-065ba4c7c253","0151194f-d918-4e72-b685-4a451c133885","88578705-23f2-449f-a1fd-a4eb0bd7d81e","cc37bb7f-09f8-444b-b852-f6340d5a304e","0a2c8585-b371-4ba1-a998-f95995cbbbb4","d5f2049d-d7cb-4664-8f79-8ff9637be6de","e391d2bd-2ee9-4d39-b82a-533766a512dc","7b99b0b3-34ef-423b-805c-32e2aa4068d0"]</t>
+  </si>
+  <si>
+    <t>e3f2cb89-0c46-4991-ab5a-e328886fafc9</t>
+  </si>
+  <si>
+    <t>["5c843eab-3e39-4759-b6c6-d22d3a65e903","7fd9a24b-af74-469f-bcd2-e3224e85058f","e8c04a2f-9f86-46c1-bf14-97e6f32fe7b2","7e398870-72b5-4ce6-92ee-fba2e98218cd","4d1897b8-27d5-48cf-84a8-e29aa273a409","ed573df4-0522-47a9-b6be-be8b7eef4dbd","31d3d9e9-e687-4817-8902-3309139bd071","afa7f2da-0c89-4bae-ba8a-6d538320c025","1f9154ce-8cf5-4bbd-9fe6-f7e27a9f7d67","d0c68a66-84c1-48e9-b863-33eb61447a2d","e552ecf8-409e-4cdb-8589-8abc02af02bb","d502260d-a294-43f5-abba-c924aca1c74b"]</t>
+  </si>
+  <si>
+    <t>d557a98c-fbaa-46a2-9e27-97ce871d7cf8</t>
+  </si>
+  <si>
+    <t>["9f59b6cf-0dc6-49fd-ab8e-c42f15983b81","806b0c9c-690e-4496-9e2a-371f518c8959"]</t>
+  </si>
+  <si>
+    <t>981a101b-caae-43c7-a83a-c31e0151c58a</t>
+  </si>
+  <si>
+    <t>["756fe53e-ed46-4802-9ccf-80c7fd46ace6","e6a46a45-e1bf-4c55-a7aa-a78ee085062c"]</t>
+  </si>
+  <si>
+    <t>47355eee-c567-4b20-aedc-90e5e05bc6fb</t>
+  </si>
+  <si>
+    <t>["0c8863b5-648d-4499-aea2-5d0c4131d724","9cb80f62-e9d5-4d00-81ba-86a086fe6af7"]</t>
+  </si>
+  <si>
+    <t>d379600b-3f53-456b-a981-4e9abc8f5997</t>
+  </si>
+  <si>
+    <t>["7ce57ecf-bd90-42a5-8c58-d78020878fa3","d90b0e83-c690-404e-bd1f-b7514e668359","78e86c76-67c5-4e2a-a503-aeafdf60e551","02a50d80-9ae7-47a2-9249-0a792fce5e19","50d10dae-2c7f-4a85-ae4a-7c44b7fa5f39","e60a6986-b868-4eeb-b82f-d71586e48b8d","e9575728-fd0e-4082-8389-275e9c51e7d2","a832e40d-bfb3-45d3-9fec-e9fd53f281d4"]</t>
+  </si>
+  <si>
+    <t>fa923af1-2e11-497f-823e-b095102a0738</t>
+  </si>
+  <si>
+    <t>["7053dcd9-839c-458b-a7ff-6833678f0fbc","964e037a-491c-4ee3-b425-82123832041b","3ffdc8be-1c7d-4261-8e28-0d76173b964a","5539a11e-2220-4d7f-8434-01e9d041f5b4"]</t>
+  </si>
+  <si>
+    <t>62d1df6b-4aec-4086-a7ab-09b4118c9ae3</t>
+  </si>
+  <si>
+    <t>["1a049d6f-bffd-48ae-a755-8184129d51a1","f6d3f6d2-d2c8-4751-911a-3c6f96eac43a","737d6056-0102-4ee8-994c-d756c8020105","cd0997cb-6c91-4e93-aaf7-a792f48cc543"]</t>
+  </si>
+  <si>
+    <t>edcd958a-696f-4474-a659-5827bc5a06c9</t>
+  </si>
+  <si>
+    <t>["a8f01dba-298d-4388-94dd-9eab0eec8237","935b7a9b-c8b9-407d-a77b-5cae86a079ea","040ff5c0-af63-4963-8812-e1a2c2c98e87","35e4e60e-c90c-4b28-a1f5-2dfdcf080325","fd31a6fd-5ab0-4b3e-bf07-a45ca8f2172a","856ee0a3-4550-4c32-8a83-9368a49ab787","45d70111-3c5f-407d-abd6-3dcc35e3f002"]</t>
+  </si>
+  <si>
+    <t>bb309645-3770-4ee9-8b2c-0e85d55b52ad</t>
+  </si>
+  <si>
+    <t>["b4d86e8c-a550-4ed6-9160-d7fba3921f4b","8c2fc825-8b72-4c21-84e2-d2be8f705780","1f1c4bb4-7dcf-4463-abd6-35140132310c","3f9ebf9b-72a0-488e-a78d-38fb40eae75a","41f32816-ec68-4dd7-9a6c-10d5cde16b50","b3bb7360-8f9c-4c54-9ecb-7896242b83fa","b2fc2b98-f3af-40fb-ac53-0eddd1e21165","cafdd370-91bf-43e3-a573-74b154fe8c84","b9350108-0204-417b-b590-2fe54117090b"]</t>
+  </si>
+  <si>
+    <t>48a88d49-120d-4f44-b6ed-066bf3630c9e</t>
+  </si>
+  <si>
+    <t>["4397c297-efec-40db-a1f2-fb3dc740b838","d99f595c-a747-408f-966e-ad905e7c4245","598655ce-2c06-4bc5-8756-12f11b5c3d2b","61a52970-9a4a-435d-9b73-ef4d63226555","0a84a7f4-53c9-4a54-93ae-4ef8e3399550"]</t>
+  </si>
+  <si>
+    <t>82ccff6c-0b84-4da2-9ea5-dcaffd1c18a1</t>
+  </si>
+  <si>
+    <t>["313000df-3603-47a0-9958-2bc9e895139f","7ed2ca5b-06ca-4541-a6bd-e1b3527b27d3","8c8c2002-45a8-494a-95dc-cd1b91a5d955","aa4a5466-e30a-4c19-ad67-e8ae92b6b08e","f9cd6ac3-57a0-4b9e-993f-2981bd6e1200","e4b00908-8e61-4264-a732-2e89bbf1d980"]</t>
+  </si>
+  <si>
+    <t>bc014ef7-3a7c-4d06-a3eb-da40c6c45434</t>
+  </si>
+  <si>
+    <t>["84a29566-fecf-4999-a1bf-7126403cd4c5","f73dcd64-b7cf-4ce3-8317-d27edadabfd7","0d45b081-ec8d-4133-8046-5af0036aa59e","efd28857-305b-4fd6-85d8-ec6e84bf808c"]</t>
+  </si>
+  <si>
+    <t>a5d4682d-1a3a-49cf-8468-2fa8dbcc9807</t>
+  </si>
+  <si>
+    <t>["ef7704e1-ed59-4f8d-9ae1-16b09bf78631","257e110a-1fbc-4db6-93f0-5515f5fb40ac"]</t>
+  </si>
+  <si>
+    <t>8af97b24-cd36-4ca2-9464-df9ba4c55038</t>
+  </si>
+  <si>
+    <t>["68474170-171e-4b5f-8c83-12ec210918be","0e495b05-032e-4bca-977e-fa8fb74fe5d4"]</t>
+  </si>
+  <si>
+    <t>232c2361-9c27-484e-add5-86dbd53b8d8b</t>
+  </si>
+  <si>
+    <t>["564ed72b-b477-49ae-b76a-3d2ab5552342","98676dda-475c-4597-bcca-67632b6a3820"]</t>
+  </si>
+  <si>
+    <t>b3c2a399-0722-446d-a339-110b8f4a3f8c</t>
+  </si>
+  <si>
+    <t>["b03f66d9-6f82-49d5-a5c6-86af33545730","c4ff5f50-43e2-4dc3-a3ab-b498da0e39f2","5e219e32-96a7-40bb-bd6c-8c236879e2bf"]</t>
+  </si>
+  <si>
+    <t>46b8609d-784d-4611-a563-4896ff0be7d0</t>
+  </si>
+  <si>
+    <t>["97e9a465-1bb8-4b58-844b-eff4f5563b6e","6a7e008e-3054-4c0d-bb84-aed47eb43152"]</t>
+  </si>
+  <si>
+    <t>b7870e32-b79e-4c5a-990d-790a5fd939d8</t>
+  </si>
+  <si>
+    <t>["11159066-0048-42c5-86f0-f4b07057a7b0","8cdb6242-f61d-4a8f-b38c-976d57a1c761"]</t>
   </si>
   <si>
     <t>chapter</t>
@@ -369,7 +369,7 @@
     <t>מחירי עבודות הפירוק כוללים הגנה על הרכוש הנותר ופינוי הפסולת הנוצרת מהפירוק. פריטים המיועדים לשימוש חוזר יזוהו בפרויקט ויפורקו לשמירה. אין לחייב שוב אותו פינוי בסעיף אחר.</t>
   </si>
   <si>
-    <t>1b2325c4-3966-498f-8366-a0f5dda84597</t>
+    <t>973d9ae9-4cec-4f7d-8439-e1ccf2352869</t>
   </si>
   <si>
     <t>note</t>
@@ -384,7 +384,7 @@
     <t>קומפ'</t>
   </si>
   <si>
-    <t>0bfab241-ed81-43ee-99b0-5526452543a7</t>
+    <t>2b24a6d4-7f01-4833-ac95-5620fb5f9d4d</t>
   </si>
   <si>
     <t>item</t>
@@ -396,7 +396,7 @@
     <t>פירוק ופינוי ריהוט קבוע, ארונות וציוד המיועדים לפינוי באזור {אזור}; פריטים לשימוש חוזר וגבולות פירוק יפורטו לפני תחילת העבודה.</t>
   </si>
   <si>
-    <t>b4a6859b-aadb-4a39-859d-136a349ec68c</t>
+    <t>7963bb1d-2a2d-4492-a854-625e02ed7ae6</t>
   </si>
   <si>
     <t>1.03</t>
@@ -408,7 +408,7 @@
     <t>מ"ר</t>
   </si>
   <si>
-    <t>5a048a3b-1e97-41e1-bbaf-f07b3e5a1af8</t>
+    <t>dd177ffd-cd7a-48ed-bcec-55f4a1d5da18</t>
   </si>
   <si>
     <t>1.04</t>
@@ -417,7 +417,7 @@
     <t>פירוק ריצוף ושכבות תשתית באזור {אזור}, עד {גבול ועומק פירוק}, כהכנה לעבודות החדשות המפורטות בפרויקט.</t>
   </si>
   <si>
-    <t>4bc42c11-c26d-4db2-9bed-59b566c56110</t>
+    <t>634ff637-2288-4579-99e2-a7b3add4f18c</t>
   </si>
   <si>
     <t>1.05</t>
@@ -426,7 +426,7 @@
     <t>פירוק מערכת חשמל ואביזריה באזור {אזור}, בגבולות הנקובים בתכנון. מעגלים ואביזרים שנשארים פעילים או מיועדים להרכבה מחדש: {פירוט}.</t>
   </si>
   <si>
-    <t>81b27a8b-b6cf-406b-9a4f-4064fd0e67ce</t>
+    <t>23dbaac1-360b-44be-84d2-46bbc399a5ea</t>
   </si>
   <si>
     <t>1.06</t>
@@ -435,7 +435,7 @@
     <t>פירוק צנרת ואביזרי אינסטלציה המיועדים להחלפה באזור {אזור}, בגבולות {תחילה וסיום}; הגנת וחסימת קצוות החיבור לפי התכנון.</t>
   </si>
   <si>
-    <t>e3f473bc-d7e6-46b1-984d-3181e8d54797</t>
+    <t>f81b49d2-e7a4-4f3f-8d58-71d9297f4464</t>
   </si>
   <si>
     <t>1.07</t>
@@ -444,7 +444,7 @@
     <t>פירוק שילוט קיים מטיפוס {זיהוי}, כולל רכיבי התקנה והזנה המיועדים לפירוק, ושמירה על רכיבים שסומנו להמשך שימוש.</t>
   </si>
   <si>
-    <t>070e4db8-dea0-48c6-956d-0c3a3be755b0</t>
+    <t>081d1ca5-39e7-4c93-9e84-f31e487fde6e</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 1 להעברה</t>
@@ -456,7 +456,7 @@
     <t>מחירי המחיצות כוללים את רכיבי המערכת, התשתית, החיבורים והגמר המוגדרים בסעיף. סוגי לוחות, שכבות, בידוד ועיגון יושלמו לפי הפרויקט. גמר צבע וחיפוי מתומחרים בפרקים המיועדים להם, אלא אם הוגדר אחרת במפורש.</t>
   </si>
   <si>
-    <t>89ec1321-ba79-4713-9bd0-0c59184ce03f</t>
+    <t>256d7b19-ad40-4c88-8eeb-59612a2b500e</t>
   </si>
   <si>
     <t>2.01</t>
@@ -468,19 +468,28 @@
     <t>מ.א.</t>
   </si>
   <si>
-    <t>e2a1ca32-0e8e-4f85-9128-d045e82423f9</t>
+    <t>39bd191e-d21e-4494-b9d1-1c8d48bf0b6f</t>
   </si>
   <si>
     <t>2.02</t>
   </si>
   <si>
+    <t>הקמת מחיצת פנים בגובה מלא באזור {אזור}, מטיפוס {טיפוס}, בגובה {גובה}, לרבות קונסטרוקציה, לוחות, חיבורים ועיגון לפי פרט {הפניה}. הרכב המחיצה, עובי, מספר שכבות ובידוד: {מפרט}. גמר צבע וחיפוי מתומחרים בנפרד.</t>
+  </si>
+  <si>
+    <t>532c0665-7ca7-49c5-bc97-18a2433bcb8b</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
     <t>ביצוע עיבוי או חיפוי קיר קיים במערכת {סוג}, בגובה {גובה}, באזור {אזור}, לצורך {ייעוד}, לרבות תשתית וחיבורים כמפורט.</t>
   </si>
   <si>
-    <t>510a2791-66f0-499a-b814-91c4e57deb43</t>
-  </si>
-  <si>
-    <t>2.03</t>
+    <t>3df0dcbc-66c2-413b-8dbe-692aa4b14962</t>
+  </si>
+  <si>
+    <t>2.04</t>
   </si>
   <si>
     <t>אספקה והתקנת מגן פינה מנירוסטה מטיפוס {טיפוס}, במידות {מידות}, עובי וגמר {מפרט}, על תשתית {סוג} ובאופן חיבור {פרט}.</t>
@@ -489,25 +498,25 @@
     <t>יח'</t>
   </si>
   <si>
-    <t>0a23b5af-82e5-46aa-bef6-7362e7c40c87</t>
-  </si>
-  <si>
-    <t>2.04</t>
+    <t>af949811-1c6f-4be8-9d86-426aa29f7171</t>
+  </si>
+  <si>
+    <t>2.05</t>
   </si>
   <si>
     <t>אספקה והתקנת מגן קצה מנירוסטה מטיפוס {טיפוס}, במידות {מידות}, עובי וגמר {מפרט}, על תשתית {סוג} ובאופן חיבור {פרט}.</t>
   </si>
   <si>
-    <t>06cac1d3-0240-43e5-ab54-96c72adc3ca0</t>
-  </si>
-  <si>
-    <t>2.05</t>
+    <t>e7105ff8-e123-4fe0-99c3-440293f1f930</t>
+  </si>
+  <si>
+    <t>2.06</t>
   </si>
   <si>
     <t>אספקה והתקנת משקוף נירוסטה לפתח {זיהוי וייעוד}, במידות {מידות}, עובי וגמר {מפרט}, לרבות החיבורים והעיגון שנקבעו לפריט.</t>
   </si>
   <si>
-    <t>f97b0dae-366b-48bf-9519-7bc170cb2766</t>
+    <t>c7cc79c7-fe11-435e-b562-a1cae8d0a0a0</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 2 להעברה</t>
@@ -516,7 +525,7 @@
     <t>מערכת המים והדלוחין תבוצע לפי תכנון הפרויקט. המחירים כוללים צנרת ואביזרי תשתית, חיבורים, הכנות ובדיקות כפי שנקבעו במפרט. אספקת כלים סניטריים וציוד אינה כלולה בסעיפי התקנה בלבד. קיום מערכת באתר אינו מעיד שאינה דורשת התאמה.</t>
   </si>
   <si>
-    <t>092f557e-3e6d-4dac-980b-fd4f0c61f9c7</t>
+    <t>155a6b9e-2d80-4526-8ed5-065ba4c7c253</t>
   </si>
   <si>
     <t>3.01</t>
@@ -525,7 +534,7 @@
     <t>ביצוע או התאמת מערכת מים ודלוחין באזור {אזור}, בין נקודות החיבור {תחילה וסיום}, לרבות {צנרת, אביזרים ומתקנים}, לפי תכנון {הפניה}. חיבור למערכת קיימת יוגדר לפי מצב האתר שנבדק.</t>
   </si>
   <si>
-    <t>2811b5de-0b50-4acf-acb4-3b5c53525d1f</t>
+    <t>0151194f-d918-4e72-b685-4a451c133885</t>
   </si>
   <si>
     <t>3.02</t>
@@ -537,7 +546,7 @@
     <t>נק'</t>
   </si>
   <si>
-    <t>0cde9a76-fa91-402d-8488-94c9c574b974</t>
+    <t>88578705-23f2-449f-a1fd-a4eb0bd7d81e</t>
   </si>
   <si>
     <t>3.03</t>
@@ -546,7 +555,7 @@
     <t>ביצוע נקודת מים קרים ודלוחין עבור {כיור או ציוד}, לפי תכנון הפרויקט, לרבות הצנרת ואביזרי החיבור בגבולות {תכולה}.</t>
   </si>
   <si>
-    <t>09dbb842-7103-4270-97e3-fc858f2b9bfa</t>
+    <t>cc37bb7f-09f8-444b-b852-f6340d5a304e</t>
   </si>
   <si>
     <t>3.04</t>
@@ -555,7 +564,7 @@
     <t>ביצוע נקודת דלוחין עצמאית עבור {ציוד או ייעוד}, לרבות חיבור וסיום לפי תכנון הפרויקט. אין לכלול שוב ניקוז שכבר נכלל בנקודת מים משולבת.</t>
   </si>
   <si>
-    <t>d85e0b12-5b80-4b4b-81e6-4447766dd4e7</t>
+    <t>0a2c8585-b371-4ba1-a998-f95995cbbbb4</t>
   </si>
   <si>
     <t>3.05</t>
@@ -564,7 +573,7 @@
     <t>ביצוע נקודת ניקוז למיזוג אוויר מטיפוס {טיפוס}, לפי תכנון המיזוג והתברואה; קצה וגבול החיבור לקבלן המיזוג: {פירוט}.</t>
   </si>
   <si>
-    <t>f9e4c395-0fcd-4cf5-8a14-9db72695105f</t>
+    <t>d5f2049d-d7cb-4664-8f79-8ff9637be6de</t>
   </si>
   <si>
     <t>3.06</t>
@@ -573,7 +582,7 @@
     <t>התקנת תעלת ניקוז מטיפוס {טיפוס}, במידות {מידות}, על התשתית המוגדרת, וחיבורה למערכת הניקוז. אספקת התעלה, עיגון ואיטום המפגש: {חלוקת אחריות}.</t>
   </si>
   <si>
-    <t>8353bc9d-b942-445e-80a8-787dea0c752e</t>
+    <t>e391d2bd-2ee9-4d39-b82a-533766a512dc</t>
   </si>
   <si>
     <t>3.07</t>
@@ -582,7 +591,7 @@
     <t>אספקה והתקנת מתקן חימום מים מסוג {סוג}, בקיבול או הספק {נתון}, עם אביזרים וחיבורים כמפורט בתכנון. גבולות עבודות החשמל ועיגון המתקן: {פירוט}.</t>
   </si>
   <si>
-    <t>0d5e5a43-8ea4-4402-99e7-ea8f9b6a714f</t>
+    <t>7b99b0b3-34ef-423b-805c-32e2aa4068d0</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 3 להעברה</t>
@@ -591,7 +600,7 @@
     <t>עבודות החשמל כוללות תשתית, מוליכים, חיבורים ואביזרים רק בתכולה המוגדרת לכל סעיף ולפי תכנון החשמל. הכנת נקודה, התקנת גוף ואספקת גוף הן תכולות שונות. חתכי מוליכים, קטרים, הגנות, הספקים ואופן הבדיקה ייקבעו בתכנון ולא יועתקו מפרויקט קודם.</t>
   </si>
   <si>
-    <t>a5538cd3-1abd-44d5-858e-058a8ab6b72d</t>
+    <t>5c843eab-3e39-4759-b6c6-d22d3a65e903</t>
   </si>
   <si>
     <t>4.01</t>
@@ -600,7 +609,7 @@
     <t>ביצוע נקודת הפעלה וחיבור למעגל תאורה מטיפוס {טיפוס}, באזור {אזור}, לפי תכנון החשמל, כולל {תשתית, חיבור ואביזרי הפעלה}. אספקת והתקנת גופי התאורה אינן נכללות בסעיף זה.</t>
   </si>
   <si>
-    <t>1b5296c6-de36-4329-b2e5-25d47b534a89</t>
+    <t>7fd9a24b-af74-469f-bcd2-e3224e85058f</t>
   </si>
   <si>
     <t>4.02</t>
@@ -609,7 +618,7 @@
     <t>ביצוע יציאה נוספת לגוף תאורה המשויך למעגל {זיהוי}, לפי תכנון החשמל; תכולת החיבור: {פירוט}.</t>
   </si>
   <si>
-    <t>73197d04-2d4d-4608-a0ca-03c64087c7f9</t>
+    <t>e8c04a2f-9f86-46c1-bf14-97e6f32fe7b2</t>
   </si>
   <si>
     <t>4.03</t>
@@ -618,7 +627,7 @@
     <t>התקנת וחיבור גוף תאורה מטיפוס {טיפוס} על תשתית {קיימת או חדשה}, לרבות אביזרי ההתקנה המוגדרים. אספקת הגוף: {אחריות}.</t>
   </si>
   <si>
-    <t>7697e26b-4e56-407f-85a7-279bb9abcaef</t>
+    <t>7e398870-72b5-4ce6-92ee-fba2e98218cd</t>
   </si>
   <si>
     <t>4.04</t>
@@ -627,7 +636,7 @@
     <t>ביצוע נקודת כוח חד־פאזית עבור {ייעוד}, באזור {אזור}, עם האביזר והתשתית לפי תכנון החשמל ובגבולות {תכולה}.</t>
   </si>
   <si>
-    <t>3098007d-3d51-4129-815b-8e2d0a8a9fc9</t>
+    <t>4d1897b8-27d5-48cf-84a8-e29aa273a409</t>
   </si>
   <si>
     <t>4.05</t>
@@ -636,7 +645,7 @@
     <t>ביצוע נקודת כוח תלת־פאזית עבור {ציוד}, לפי מפרט ההזנה של מתכנן החשמל ויצרן הציוד. אביזר החיבור וגבול העבודה: {פירוט}.</t>
   </si>
   <si>
-    <t>69f96b77-f6b6-4c7d-ad66-ecbca9ded3e3</t>
+    <t>ed573df4-0522-47a9-b6be-be8b7eef4dbd</t>
   </si>
   <si>
     <t>4.06</t>
@@ -645,7 +654,7 @@
     <t>ביצוע נקודת הזנה למיזוג אוויר עבור {יחידה}, בהתאם לתכנון החשמל והמיזוג, לרבות אביזר סיום וגבול חיבור {פירוט}.</t>
   </si>
   <si>
-    <t>1cd83078-58d3-4fa8-8e49-45b89032bcbf</t>
+    <t>31d3d9e9-e687-4817-8902-3309139bd071</t>
   </si>
   <si>
     <t>4.07</t>
@@ -654,7 +663,7 @@
     <t>ביצוע נקודת הזנה למפוח עבור {יחידה וייעוד}, בהתאם לתכנון החשמל והאוורור, לרבות אביזר סיום וגבול חיבור {פירוט}.</t>
   </si>
   <si>
-    <t>b8e01dec-be46-41c0-8713-a61f281f92fd</t>
+    <t>afa7f2da-0c89-4bae-ba8a-6d538320c025</t>
   </si>
   <si>
     <t>4.08</t>
@@ -663,7 +672,7 @@
     <t>ביצוע תשתית תקשורת מטיפוס {סוג}, בין נקודות {קצוות}, לרבות צנרת, חוט משיכה ואביזרי סיום שנקבעו. כבילה פעילה וציוד קצה: {תכולה ואחריות}.</t>
   </si>
   <si>
-    <t>9b4db498-670d-4e7c-b392-976f68575547</t>
+    <t>1f9154ce-8cf5-4bbd-9fe6-f7e27a9f7d67</t>
   </si>
   <si>
     <t>4.09</t>
@@ -672,7 +681,7 @@
     <t>אספקה והתקנת לוח חשמל {זיהוי}, כולל מכלול הרכיבים, הסימון, החיווט והחיבור שנקבעו בתכנון החשמל. גודל החיבור והמפרט יושלמו בפרויקט.</t>
   </si>
   <si>
-    <t>b42e0cb8-4764-4c95-9206-a702a3ca94fa</t>
+    <t>d0c68a66-84c1-48e9-b863-33eb61447a2d</t>
   </si>
   <si>
     <t>4.10</t>
@@ -681,7 +690,22 @@
     <t>ביצוע הזנת חשמל והפעלה לשלט {זיהוי}, לרבות מעבר כבל בתשתית המוגדרת וחיבור בנקודת הסיום {מיקום}. השלט וספקו יתומחרו בנפרד אלא אם צוינה תכולה אחרת.</t>
   </si>
   <si>
-    <t>880cc642-297a-42d8-b61f-31afc044a081</t>
+    <t>e552ecf8-409e-4cdb-8589-8abc02af02bb</t>
+  </si>
+  <si>
+    <t>חשמל והכנות תקשורת (המשך)</t>
+  </si>
+  <si>
+    <t>heading</t>
+  </si>
+  <si>
+    <t>4.11</t>
+  </si>
+  <si>
+    <t>ביצוע תאורת חירום באזור {אזור}, לפי תכנון היועץ {הפניה}, בתכולה {פירוט המערכת והעבודות}. אספקת הגופים, התקנתם, ההזנות והחיבורים: {חלוקת אחריות ותכולה}. רכיבים המתומחרים בסעיפים אחרים יוחרגו במפורש.</t>
+  </si>
+  <si>
+    <t>d502260d-a294-43f5-abba-c924aca1c74b</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 4 להעברה</t>
@@ -690,7 +714,7 @@
     <t>הכנת רצפה והגבהה יפורטו רק כשנדרשות בפרויקט. יש להגדיר גבול בין הכנת המשטח, איטום וריצוף, בלי לחייב אותה שכבה פעמיים. חומר, עומס ומפלסים ייקבעו בתכנון המאושר.</t>
   </si>
   <si>
-    <t>8eb99a66-c8da-4a85-a2e8-263b4882b200</t>
+    <t>9f59b6cf-0dc6-49fd-ab8e-c42f15983b81</t>
   </si>
   <si>
     <t>5.01</t>
@@ -699,7 +723,7 @@
     <t>ביצוע שכבת הכנה, מילוי או הגבהה באזור {אזור}, מחומר {מערכת}, בעובי ובמפלס {נתונים}, לרבות {תשתית, גמר והשלמות נכללים}, לפי פרט מאושר.</t>
   </si>
   <si>
-    <t>bf62f5ce-1eac-4520-b186-93108dfcdd4e</t>
+    <t>806b0c9c-690e-4496-9e2a-371f518c8959</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 5 להעברה</t>
@@ -708,7 +732,7 @@
     <t>מערכת האיטום תיקבע לפי התשתית, השימוש, החדירות והמפגשים בפרויקט. כל סעיף יפרט את הכנת התשתית, סיומות, טיפול בנקזים ובפתחים ובדיקות נדרשות. אין ברירת מחדל לשיטת איטום, עובי, גובה רולקה או מותג.</t>
   </si>
   <si>
-    <t>c29540f3-d119-4395-bc60-4274c439e0e2</t>
+    <t>756fe53e-ed46-4802-9ccf-80c7fd46ace6</t>
   </si>
   <si>
     <t>6.01</t>
@@ -717,7 +741,7 @@
     <t>ביצוע איטום באזור רטוב {זיהוי ואזור}, במערכת {מפרט מאושר}, לרבות הכנת תשתית, מפגשי קיר ורצפה, חדירות וסיומות לפי הפרט. בדיקות ותכולת ההכנה: {פירוט}.</t>
   </si>
   <si>
-    <t>3df8333e-a3b0-4391-9a1e-b3d44e5439aa</t>
+    <t>e6a46a45-e1bf-4c55-a7aa-a78ee085062c</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 6 להעברה</t>
@@ -726,7 +750,7 @@
     <t>מחיר כל טיפוס דלת כולל כנף, משקוף, הלבשות, פרזול, גמר, הובלה והרכבה לפי תיאור הסעיף. סוגי מילוי, צירים, פתיחה והתאמת נגישות או בטיחות יוגדרו בפרויקט; אין הוראה כללית של פרזול הסותרת טיפוס דלת.</t>
   </si>
   <si>
-    <t>59988ad9-fe8c-426c-b71f-00890db727f8</t>
+    <t>0c8863b5-648d-4499-aea2-5d0c4131d724</t>
   </si>
   <si>
     <t>7.01</t>
@@ -736,7 +760,7 @@
 מידות ופתיחה: {מידות וכיוון}; כנף ומילוי: {מפרט}; משקוף והלבשות: {מפרט}; פרזול: {מפרט}; גמר וגוון: {מפרט}; תכנית ופרט: {הפניה}.</t>
   </si>
   <si>
-    <t>da179852-7c12-45bc-bd39-523c09d68224</t>
+    <t>9cb80f62-e9d5-4d00-81ba-86a086fe6af7</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 7 להעברה</t>
@@ -745,16 +769,16 @@
     <t>מחירי עבודות הריצוף והחיפוי כוללים הכנת תשתית בתכולה שנקבעה, חומרי עזר, חיתוכים, התאמות, פינות ורובה בהתאם למפרט. אספקת האריחים תתומחר בפרק האספקות כשאינו כבוי; פנלים המופיעים בסעיף נפרד אינם כלולים שוב במחיר השטח.</t>
   </si>
   <si>
-    <t>2706522f-38a0-44a0-8be9-f9afa33c4b6e</t>
+    <t>7ce57ecf-bd90-42a5-8c58-d78020878fa3</t>
   </si>
   <si>
     <t>8.01</t>
   </si>
   <si>
-    <t>ריצוף אזור הכנת המזון ופנים הדלפק {אזור}, באריחי גרניט פורצלן אנטיסליפ במידות 30×30 ס״מ, עם מישקים 3 מ״מ ורובה אפוקסית שחורה. דרגת ההחלקה ודגם האריח {בחירה לפי שימוש ותכנון הסניף; אינם מפורטים במקור דובאי}. מפגשים, שיפועים ונקזים לפי פרט {הפניה}; אספקת האריחים {אחריות}.</t>
-  </si>
-  <si>
-    <t>f88046c6-21f1-4ac8-b189-b2dafa348bf3</t>
+    <t>ריצוף אזור הכנת המזון ופנים הדלפק {אזור}, באריחי גרניט פורצלן אנטיסליפ במידות 30×30 ס״מ, עם מישקים 3 מ״מ ורובה אפוקסית שחורה. דרגת ההחלקה ודגם האריח {בחירה לפי שימוש ותכנון הסניף}. מפגשים, שיפועים ונקזים לפי פרט {הפניה}; אספקת האריחים {אחריות}.</t>
+  </si>
+  <si>
+    <t>d90b0e83-c690-404e-bd1f-b7514e668359</t>
   </si>
   <si>
     <t>8.02</t>
@@ -763,7 +787,7 @@
     <t>חיפוי דופן חיצונית של דלפק {זיהוי}, בחומר {סוג, דגם ומידה}, בדוגמה ובגמר {פירוט}, על תשתית {סוג}; פרופילים וחיבוריהם נכללים רק לפי התכולה המפורשת.</t>
   </si>
   <si>
-    <t>8529bf7c-eaf0-4510-b50c-306442581bce</t>
+    <t>78e86c76-67c5-4e2a-a503-aeafdf60e551</t>
   </si>
   <si>
     <t>8.03</t>
@@ -772,7 +796,7 @@
     <t>חיפוי דופן פנימית לדלפק {זיהוי}, באריחי קרמיקה לבנה במידות 30×60 ס״מ, עם מישקים 3 מ״מ ורובה כחולה, לגובה {גובה}, על תשתית {סוג}. אספקת האריחים {אחריות}. אין לכלול חיפוי פורמייקה באותו שטח.</t>
   </si>
   <si>
-    <t>64b035af-4601-4388-93ca-c94bc58dff83</t>
+    <t>02a50d80-9ae7-47a2-9249-0a792fce5e19</t>
   </si>
   <si>
     <t>8.04</t>
@@ -781,7 +805,7 @@
     <t>התקנת פנל תואם לריצוף {חומר וגמר}, בגובה {גובה}, לאורך האזור {אזור}, לרבות פינות וסיומות לפי הפרט.</t>
   </si>
   <si>
-    <t>cd04e3f9-8ca9-4f41-a059-6e5c1b8b115f</t>
+    <t>50d10dae-2c7f-4a85-ae4a-7c44b7fa5f39</t>
   </si>
   <si>
     <t>8.05</t>
@@ -790,16 +814,25 @@
     <t>חיפוי קירות מטבח באזור {אזור}, באריחי קרמיקה לבנה מבריקה במידות 30×60 ס״מ, עם מישקים 2 מ״מ ורובה לבנה, לגובה {גובה לפי הסניף}. אספקת האריחים {אחריות}; פינות ומפגשים לפי פרט {הפניה}.</t>
   </si>
   <si>
-    <t>b0c8b859-961f-4ae0-8753-f22a36c4b5ed</t>
+    <t>e60a6986-b868-4eeb-b82f-d71586e48b8d</t>
   </si>
   <si>
     <t>8.06</t>
   </si>
   <si>
+    <t>חיפוי קיר באזור {אזור}, באריחים דמויי בטון במידות 120×60 ס"מ, לגובה {גובה}, על תשתית {סוג}. דגם וגמר האריח, מישקים ורובה: {מפרט}. פינות ומפגשים לפי פרט {הפניה}; אספקת האריחים: {אחריות}.</t>
+  </si>
+  <si>
+    <t>e9575728-fd0e-4082-8389-275e9c51e7d2</t>
+  </si>
+  <si>
+    <t>8.07</t>
+  </si>
+  <si>
     <t>ריצוף אזור ישיבה או שטח ציבורי {אזור}, כשנכלל בסניף, באריחי גרניט פורצלן דמוי טרצו במידות 80×80 ס״מ, עם מישקים 2 מ״מ ורובה אפורה, על תשתית {סוג}. אספקת האריחים {אחריות}.</t>
   </si>
   <si>
-    <t>b36f8fc7-83c3-4bbd-9c96-8427d842fcd9</t>
+    <t>a832e40d-bfb3-45d3-9fec-e9fd53f281d4</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 8 להעברה</t>
@@ -808,25 +841,34 @@
     <t>המחירים כוללים תשתית, תלייה, חיבורים, פרופילי גמר ופתחים למערכות לפי מפרט התקרה. יש להגדיר סוג לוח או אריח, גובה, טיפול אקוסטי וחיזוקים. גמר צבע מתומחר בנפרד אם אינו מפורש כחלק מהמוצר.</t>
   </si>
   <si>
-    <t>c5d5a26a-cdf1-414b-99d6-4f6d5a6037df</t>
+    <t>7053dcd9-839c-458b-a7ff-6833678f0fbc</t>
   </si>
   <si>
     <t>9.01</t>
   </si>
   <si>
+    <t>אספקה והתקנת הנמכת תקרת גבס באזור {אזור}, בגובה ובחלוקה {נתונים}, מלוחות {סוג, עובי ומספר שכבות}, לרבות קונסטרוקציה, תלייה, חיבורים, פרופילי גמר ופתחים למערכות לפי תכנית ופרט {הפניה}. חיזוקים וטיפול אקוסטי: {מפרט לפי הצורך}. גמר צבע מתומחר בנפרד.</t>
+  </si>
+  <si>
+    <t>964e037a-491c-4ee3-b425-82123832041b</t>
+  </si>
+  <si>
+    <t>9.02</t>
+  </si>
+  <si>
     <t>ביצוע קרניז מטיפוס {טיפוס}, בחתך ובגובה {מידות}, באזור {אזור}, לרבות הכנה לתאורה או למיזוג לפי הפרט וללא אספקת גוף התאורה.</t>
   </si>
   <si>
-    <t>791d629c-829a-4192-af58-0003592fb5d4</t>
-  </si>
-  <si>
-    <t>9.02</t>
+    <t>3ffdc8be-1c7d-4261-8e28-0d76173b964a</t>
+  </si>
+  <si>
+    <t>9.03</t>
   </si>
   <si>
     <t>אספקה והתקנת תקרת מגשים ברוחב 30 ס״מ באזור מטבח או מחסן {אזור}, בגמר לבן RAL 9010 ופרופיל סיום L, לרבות תשתית ותלייה ופתחים לפי התכנון. גובה, חלוקה ועובי מגש {לפי תכנון הסניף}.</t>
   </si>
   <si>
-    <t>d7028dfd-f9c5-47fc-9546-314b8c314e0b</t>
+    <t>5539a11e-2220-4d7f-8434-01e9d041f5b4</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 9 להעברה</t>
@@ -835,7 +877,7 @@
     <t>עבודות הצבע כוללות הכנת תשתית, תיקונים וחומרי יסוד לפי המשטח והוראות המוצר. גמר קירות ותקרות אקריליים: סופרקריל, שתי שכבות לפחות ועד כיסוי מלא, גוון אפור Dunn Edwards Paints DE6374. קרניזי גל: צבע שמן מט משי בגוון כחול RAL 5012 בסעיף נפרד. המוצרים והגוונים משויכים למשטח המפורט, ללא העתקת הוראות דילול בטרפנטין. גוון אינו מחליף התאמת מוצר הצבע לתשתית.</t>
   </si>
   <si>
-    <t>933649d2-61ca-4673-9bd0-9bf2dda9ad08</t>
+    <t>1a049d6f-bffd-48ae-a755-8184129d51a1</t>
   </si>
   <si>
     <t>10.01</t>
@@ -844,7 +886,7 @@
     <t>הכנת וצביעת קירות באזור {אזור}, לרבות תיקוני תשתית והחלקה {תכולה}, בצבע אקרילי מסוג סופרקריל בשתי שכבות לפחות ועד כיסוי מלא; גוון אפור Dunn Edwards Paints DE6374. חומר יסוד לפי המשטח והוראות המוצר.</t>
   </si>
   <si>
-    <t>ba766927-4f03-4179-92d8-6c6e51f354b3</t>
+    <t>f6d3f6d2-d2c8-4751-911a-3c6f96eac43a</t>
   </si>
   <si>
     <t>10.02</t>
@@ -853,7 +895,7 @@
     <t>הכנת וצביעת תקרות גבס והנמכות באזור {אזור}, לרבות תיקוני תשתית ושפכטל אמריקאי עד החלקה, בצבע אקרילי מסוג סופרקריל בשתי שכבות לפחות ועד כיסוי מלא; גוון אפור Dunn Edwards Paints DE6374. חומר יסוד לפי המשטח והוראות המוצר.</t>
   </si>
   <si>
-    <t>df5a3fb5-c708-48a4-b3fb-4eeb6877449f</t>
+    <t>737d6056-0102-4ee8-994c-d756c8020105</t>
   </si>
   <si>
     <t>10.03</t>
@@ -862,16 +904,16 @@
     <t>הכנת וצביעת קרניז גל באזור {אזור}, לרבות תיקוני תשתית ושפכטל אמריקאי עד החלקה, בצבע שמן מט משי בשתי שכבות לפחות ועד כיסוי מלא, בגוון כחול RAL 5012. מידות ומיקום הקרניז {לפי תכנון הסניף}. אין לחייב שוב גמר צבע שנכלל במחיר קרניז מוגמר.</t>
   </si>
   <si>
-    <t>02ac2483-3766-4e87-9642-a7538fa09b5e</t>
+    <t>cd0997cb-6c91-4e93-aaf7-a792f48cc543</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 10 להעברה</t>
   </si>
   <si>
-    <t>מחיר כל פריט נגרות כולל חומרים, פרזול, גמר, הובלה והרכבה שפורטו. לוחות עץ לבוד בעובי 18 מ״מ בציפוי פורמייקה בגמר נירוסטה מוברשת D2178; עץ מסיבי במבוק בגמר לכה מט משי 15% ברק; רכיבי MDF דקורטיביים בגמר כחול RAL 5012. אין חלופת בירמן 1100 או חזית אלון מולבן כברירת מחדל. מידות כלליות, חלוקה ומפלסים לפי הסניף. רכיבי מתכת, קוריאן, זיגוג ושילוט בסעיפים נפרדים מוחרגים.</t>
-  </si>
-  <si>
-    <t>77077759-eca1-4237-b460-2fedc4e61575</t>
+    <t>מחיר כל פריט נגרות כולל חומרים, פרזול, גמר, הובלה והרכבה שפורטו. לוחות עץ לבוד בעובי 18 מ"מ בציפוי פורמייקה בירמן 1100; עץ מסיבי במבוק בגמר לכה מט משי 15% ברק; רכיבי MDF דקורטיביים בגמר כחול RAL 5012. מידות כלליות, חלוקה ומפלסים לפי הסניף. רכיבי מתכת, קוריאן, זיגוג ושילוט בסעיפים נפרדים מוחרגים.</t>
+  </si>
+  <si>
+    <t>a8f01dba-298d-4388-94dd-9eab0eec8237</t>
   </si>
   <si>
     <t>11.01</t>
@@ -880,25 +922,25 @@
     <t>אספקה והתקנת משטח מדורג להגשה לדלפק {זיהוי}, מעץ מסיבי במבוק בעובי 2 ס״מ וברוחב 26 ס״מ, עם קנט קדמי ואחורי לפי הפרט, בגמר לכה מט משי 15% ברק. אורך, צורה ומפלסים {לפי תכנון הסניף}. שלד מסגרות, דפנות וקוריאן מתומחרים בנפרד.</t>
   </si>
   <si>
-    <t>5e73d0f2-1aab-4b35-9404-644e8e8734ab</t>
+    <t>935b7a9b-c8b9-407d-a77b-5cae86a079ea</t>
   </si>
   <si>
     <t>11.02</t>
   </si>
   <si>
-    <t>אספקה והתקנת דופן פנימית לדלפק {זיהוי}, מלוחות עץ לבוד בעובי 18 מ״מ מצופים פורמייקה D2178 בגמר נירוסטה מוברשת, על שלד המתומחר בנפרד, לרבות פתחים והתאמות לציוד. גובה וחלוקה {מידות הסניף}. אין לחייב גם חיפוי קרמי באותו שטח.</t>
-  </si>
-  <si>
-    <t>adb34e5f-abfc-49e2-9d76-19db9e87e7d4</t>
+    <t>אספקה והתקנת דופן פנימית לדלפק {זיהוי}, מלוחות עץ לבוד בעובי 18 מ"מ מצופים פורמייקה בירמן 1100, על שלד המתומחר בנפרד, לרבות פתחים והתאמות לציוד. גובה וחלוקה {מידות הסניף}. אין לחייב גם חיפוי קרמי באותו שטח.</t>
+  </si>
+  <si>
+    <t>040ff5c0-af63-4963-8812-e1a2c2c98e87</t>
   </si>
   <si>
     <t>11.03</t>
   </si>
   <si>
-    <t>אספקה והתקנת דופן נגרות דקורטיבית לדלפק {זיהוי}, עשויה לוחות וסרגלי MDF בגמר צבע כחול RAL 5012, בגובה ובחלוקה {מידות הסניף}, על שלד מתומחר בנפרד. אין להחליף בחזית אלון מולבן מן המקורות הישנים. אריחים ורכיבי מיתוג בסעיפים נפרדים אינם כלולים.</t>
-  </si>
-  <si>
-    <t>870e4611-5e0d-4302-b0d6-c9129b6ab79d</t>
+    <t>אספקה והתקנת דופן נגרות דקורטיבית לדלפק {זיהוי}, עשויה לוחות וסרגלי MDF בגמר צבע כחול RAL 5012, בגובה ובחלוקה {מידות הסניף}, על שלד מתומחר בנפרד. אריחים ורכיבי מיתוג בסעיפים נפרדים אינם כלולים.</t>
+  </si>
+  <si>
+    <t>35e4e60e-c90c-4b28-a1f5-2dfdcf080325</t>
   </si>
   <si>
     <t>11.04</t>
@@ -907,7 +949,7 @@
     <t>אספקה והתקנת שער כניסה לדלפק {זיהוי}, מלוח MDF בגמר לבן ופס עליון מעץ מסיבי במבוק בחתך 4×5 ס״מ, בגמר לכה מט משי 15% ברק לרכיב הבמבוק, לרבות צירים וסגירה לפי פרט {הפניה}. מידות פתח וכיוון פתיחה {לפי הסניף}.</t>
   </si>
   <si>
-    <t>f4c2e9cd-a657-4712-810c-af158ce59e1a</t>
+    <t>fd31a6fd-5ab0-4b3e-bf07-a45ca8f2172a</t>
   </si>
   <si>
     <t>11.05</t>
@@ -916,7 +958,7 @@
     <t>התקנת לוחות תשתית לדופן דלפק {זיהוי}, מחומר ובעובי {מפרט}, על גבי {תשתית}, כהכנה לחיפוי {חומר}. החיפוי הסופי מתומחר בפרק הריצוף והחיפוי או בפרק המשטחים.</t>
   </si>
   <si>
-    <t>b8f78421-12e0-4c9a-a585-05d1131e0c5d</t>
+    <t>856ee0a3-4550-4c32-8a83-9368a49ab787</t>
   </si>
   <si>
     <t>11.06</t>
@@ -925,7 +967,7 @@
     <t>אספקה והתקנת רקע נגרות לקיר מיתוג {זיהוי}, מלוחות MDF פריקים על קורות עץ 40×40 מ״מ כהרחקה מהקיר, בחלוקה לריבועים באמצעות סרגלי MDF ‏60×20 מ״מ, בגמר כחול RAL 5012. מידות כלליות וחלוקה {לפי הסניף}. אותיות LED, ספקים והזנה מתומחרים בנפרד.</t>
   </si>
   <si>
-    <t>9e0af212-d35f-4346-bd50-afbe618ec86a</t>
+    <t>45d70111-3c5f-407d-abd6-3dcc35e3f002</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 11 להעברה</t>
@@ -934,7 +976,7 @@
     <t>עבודות המסגרות כוללות חומרי גלם, חיבורים, עיגון, הכנת שטח, חומרי יסוד וגמר המפורטים לפריט, הובלה והרכבה. לשלד דלפק פנימי: פרופיל פלדה 40×40 מ״מ וגמר שחור מט RAL 9005; עובי דופן, הגנת קורוזיה וחיבורים לפי תכנון הסניף. כחול RAL 5012 חל רק ברכיבים שסומנו כחולים בפרט המאושר. רכיבי נגרות, קוריאן, זכוכית ותאורה בסעיפים נפרדים מוחרגים.</t>
   </si>
   <si>
-    <t>43534dfe-d369-429c-b2f9-469d130c9b7e</t>
+    <t>b4d86e8c-a550-4ed6-9160-d7fba3921f4b</t>
   </si>
   <si>
     <t>12.01</t>
@@ -943,7 +985,7 @@
     <t>אספקה והתקנת שלד מסגרות פנימי לדלפק {זיהוי}, מפרופילי פלדה 40×40 מ״מ, בגמר שחור מט RAL 9005, בגובה ובחלוקה {מידות}, לרבות עיגון והכנות למעבר תשתיות לפי תכנון {הפניה}. עובי דופן והגנת קורוזיה {מפרט תכנון}. נגרות, אריחים, קוריאן וזכוכית אינם כלולים.</t>
   </si>
   <si>
-    <t>a4701464-123d-44f4-9e1a-a2d784fb3481</t>
+    <t>8c2fc825-8b72-4c21-84e2-d2be8f705780</t>
   </si>
   <si>
     <t>12.02</t>
@@ -952,7 +994,7 @@
     <t>אספקה והתקנת יחידת מדפי מתכת או מתקן תצוגה מטיפוס {טיפוס}, במידות {מידות}, מפרופילים ומשטחים {מפרט}, בגמר {גמר}, לרבות תלייה או עיגון המוגדרים לפריט.</t>
   </si>
   <si>
-    <t>8176c706-3602-4bd6-93e6-7e85344bb0fe</t>
+    <t>1f1c4bb4-7dcf-4463-abd6-35140132310c</t>
   </si>
   <si>
     <t>12.03</t>
@@ -961,7 +1003,7 @@
     <t>אספקה והתקנת מסגרת תמיכה לפריט {זיהוי}, במידות {מידות}, מפרופילים ובגמר {מפרט}, לרבות עיגון והכנות כמפורט. הפריט הנתמך מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>d30dc058-e754-42aa-930d-fdf9936518c9</t>
+    <t>3f9ebf9b-72a0-488e-a78d-38fb40eae75a</t>
   </si>
   <si>
     <t>12.04</t>
@@ -970,49 +1012,46 @@
     <t>אספקה והתקנת מסגרת תומכת לשילוט בהיקף דלפק {זיהוי}, במידות ובפרופילים {מפרט}, לרבות עיגון והכנה למעבר הזנה. אותיות, תאורה ושלט גמר אינם כלולים.</t>
   </si>
   <si>
-    <t>240649a4-986b-4ea3-91f7-bb92df91dfd1</t>
+    <t>41f32816-ec68-4dd7-9a6c-10d5cde16b50</t>
   </si>
   <si>
     <t>12.05</t>
   </si>
   <si>
-    <t>אספקה והתקנת שלד מפרופיל מגולוון 40×40 מ״מ בגמר טבעי לתמיכת מעטפת Alucobond באזור {זיהוי}, לפי תכנון ואישור מהנדס {הפניה}. אורך, גובה ועובי דופן {לפי הסניף}; לוחות הגמר מתומחרים בנפרד.</t>
-  </si>
-  <si>
-    <t>4087d0f4-41bf-46d9-92cb-1a32f43550c4</t>
+    <t>אספקה והתקנת שלד מפרופיל מגולוון 40×40 מ״מ בגמר טבעי לתמיכת מעטפת אלוקובונד באזור {זיהוי}, לפי תכנון ואישור מהנדס {הפניה}. אורך, גובה ועובי דופן {לפי הסניף}; לוחות הגמר מתומחרים בנפרד.</t>
+  </si>
+  <si>
+    <t>b3bb7360-8f9c-4c54-9ecb-7896242b83fa</t>
   </si>
   <si>
     <t>12.06</t>
   </si>
   <si>
-    <t>אספקה והתקנת לוחות Alucobond חלקים ברוחב 42 ס״מ, עם נתק 2 ס״מ בין הלוחות, בגמר כחול RAL 5012, על גבי שלד המתומחר בנפרד. גובה ואורך המעטפת {לפי הסניף}; עובי לוח {פרט תכנון, אינו מפורט במקור}. פרספקס ותאורה מתומחרים בנפרד.</t>
-  </si>
-  <si>
-    <t>e062b74d-4237-47e0-a444-785c70dd1ce0</t>
+    <t>אספקה והתקנת לוחות אלוקובונד חלקים ברוחב 42 ס״מ, עם נתק 2 ס״מ בין הלוחות, בגמר כחול RAL 5012, על גבי שלד המתומחר בנפרד. גובה ואורך המעטפת {לפי הסניף}; עובי לוח {פרט תכנון}. פרספקס ותאורה מתומחרים בנפרד.</t>
+  </si>
+  <si>
+    <t>b2fc2b98-f3af-40fb-ac53-0eddd1e21165</t>
   </si>
   <si>
     <t>12.07</t>
   </si>
   <si>
-    <t>אספקה והתקנת לוחות Alucobond מחוררים ברוחב 42 ס״מ, עם נתק 2 ס״מ בין הלוחות, בגמר כחול RAL 5012, על גבי שלד המתומחר בנפרד. גובה ואורך המעטפת {לפי הסניף}; עובי לוח {פרט תכנון, אינו מפורט במקור}. פרספקס ותאורה מתומחרים בנפרד.</t>
-  </si>
-  <si>
-    <t>cb910325-b9f3-453d-b7e0-9cf6dfb5954f</t>
+    <t>אספקה והתקנת לוחות אלוקובונד מחוררים ברוחב 42 ס״מ, עם נתק 2 ס״מ בין הלוחות, בגמר כחול RAL 5012, על גבי שלד המתומחר בנפרד. גובה ואורך המעטפת {לפי הסניף}; עובי לוח {פרט תכנון}. פרספקס ותאורה מתומחרים בנפרד.</t>
+  </si>
+  <si>
+    <t>cafdd370-91bf-43e3-a573-74b154fe8c84</t>
   </si>
   <si>
     <t>מסגרות ביפרש (המשך)</t>
   </si>
   <si>
-    <t>heading</t>
-  </si>
-  <si>
     <t>12.08</t>
   </si>
   <si>
     <t>אספקה והתקנת פרופיל הפרדה דקורטיבי מאלומיניום מכופף 80×50 מ״מ, בגמר לבן RAL 9003, בין אזורי מעטפת {זיהוי}. אורך ועיגון {לפי פרט הסניף}.</t>
   </si>
   <si>
-    <t>bc375460-a6ad-443b-9283-39151afa9d58</t>
+    <t>b9350108-0204-417b-b590-2fe54117090b</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 12 להעברה</t>
@@ -1021,7 +1060,7 @@
     <t>לחופת הדלפק ולמדף הפנימי: זכוכית מחוסמת שקופה 10 מ״מ. חופה ומדף מתומחרים בנפרד. המחיר כולל את הפרזול, התמיכות והחיבורים המוגדרים לפריט; אורך וצורת הדלפק מותאמים לסניף. זיגוג אחר אינו נכלל אוטומטית במפרט החופה.</t>
   </si>
   <si>
-    <t>c2ddd13f-b748-4789-bcfb-fc799a945e39</t>
+    <t>4397c297-efec-40db-a1f2-fb3dc740b838</t>
   </si>
   <si>
     <t>13.01</t>
@@ -1030,7 +1069,7 @@
     <t>אספקה והתקנת חופת זכוכית לדלפק {זיהוי}, מזכוכית מחוסמת שקופה בעובי 10 מ״מ, ברוחב 60 ס״מ ובגובה 40 ס״מ, לרבות דפנות, פרזול וחיבור לפי הפרט. אורך, תוואי ופינות {לפי הסניף}; מדף פנימי מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>0758be5f-dc5e-49e8-82f8-e9f756071631</t>
+    <t>d99f595c-a747-408f-966e-ad905e7c4245</t>
   </si>
   <si>
     <t>13.02</t>
@@ -1039,7 +1078,7 @@
     <t>אספקה והתקנת מדף פנימי בחופת דלפק {זיהוי}, מזכוכית מחוסמת שקופה בעובי 10 מ״מ וברוחב 35 ס״מ, לרבות תמיכות וחיבור לפי הפרט. אורך וגובה התקנה {לפי הסניף}.</t>
   </si>
   <si>
-    <t>d5a0f1f9-7ef0-4b71-a688-57ad080ad214</t>
+    <t>598655ce-2c06-4bc5-8756-12f11b5c3d2b</t>
   </si>
   <si>
     <t>13.03</t>
@@ -1048,16 +1087,16 @@
     <t>אספקה והתקנת לוח זיגוג מטיפוס {זיהוי}, במידות {מידות}, בסוג ובעובי {מפרט}, לרבות חיבורים ופרזול שנקבעו לפרט. שלד המסגרת מתומחר בנפרד ככל שהוגדר בפרק המסגרות.</t>
   </si>
   <si>
-    <t>862377fd-42e5-4b4c-b6d1-f8abddcc938e</t>
+    <t>61a52970-9a4a-435d-9b73-ef4d63226555</t>
   </si>
   <si>
     <t>13.04</t>
   </si>
   <si>
-    <t>אספקה והתקנת לוחות פרספקס חלבי בעובי 4 מ״מ ובגובה 80 ס״מ בגב לוחות Alucobond מחוררים, כהכנה לתאורת LED אחורית. אורך וחלוקה {לפי הסניף}; שלד, Alucobond, גוף תאורה והזנה מתומחרים בנפרד.</t>
-  </si>
-  <si>
-    <t>1bcf48e6-a29b-4913-83b9-671bd262ab26</t>
+    <t>אספקה והתקנת לוחות פרספקס חלבי בעובי 4 מ״מ ובגובה 80 ס״מ בגב לוחות אלוקובונד מחוררים, כהכנה לתאורת LED אחורית. אורך וחלוקה {לפי הסניף}; שלד, אלוקובונד, גוף תאורה והזנה מתומחרים בנפרד.</t>
+  </si>
+  <si>
+    <t>0a84a7f4-53c9-4a54-93ae-4ef8e3399550</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 13 להעברה</t>
@@ -1066,7 +1105,7 @@
     <t>מפרט משטחים ודפנות: Corian בגוון/דגם Glacier White; משטח פנים 8 מ״מ, דפנות מדורגות 12 מ״מ וקופינג 40 מ״מ. המחירים כוללים עיבוד, פתחים, קנטים, פינות מעוגלות, הובלה והרכבה כמפורט. אורך ותוואי לפי הסניף. אין לחייב שוב אותם משטחים בנגרות או בציוד.</t>
   </si>
   <si>
-    <t>b2b4daf5-d986-428a-b4e5-096166af4a0a</t>
+    <t>313000df-3603-47a0-9958-2bc9e895139f</t>
   </si>
   <si>
     <t>14.01</t>
@@ -1075,7 +1114,7 @@
     <t>אספקה והתקנת משטח עבודה Corian Glacier White בעובי 8 מ״מ, ברוחב 65–70 ס״מ, בפנים הדלפק או אי העבודה {זיהוי}, מעל משטחי העבודה והמקררים, כולל פתחים והתאמות לציוד. אורך ותוואי {לפי הסניף}.</t>
   </si>
   <si>
-    <t>708ecb63-c3dc-40a7-a346-a91f5ad2bdf3</t>
+    <t>7ed2ca5b-06ca-4541-a6bd-e1b3527b27d3</t>
   </si>
   <si>
     <t>14.02</t>
@@ -1084,7 +1123,7 @@
     <t>אספקה והתקנת דופן מדורגת Corian Glacier White בעובי 12 מ״מ וברוחב 26 ס״מ, עם פינות מעוגלות, על מסגרת מתכת המתומחרת בנפרד, באזור {זיהוי}. אורך ותוואי {לפי הסניף}.</t>
   </si>
   <si>
-    <t>c134bfb7-939b-496a-9e70-8a6a7a3d96c5</t>
+    <t>8c8c2002-45a8-494a-95dc-cd1b91a5d955</t>
   </si>
   <si>
     <t>14.03</t>
@@ -1093,7 +1132,7 @@
     <t>אספקה והתקנת קופינג Corian Glacier White בעובי 40 מ״מ וברוחב 20 ס״מ, עם פינות מעוגלות, על מחיצה מוגבהת בהיקף דלפק {זיהוי}. אורך ותוואי {לפי הסניף}; התשתית מתומחרת בנפרד.</t>
   </si>
   <si>
-    <t>57282de5-e5a7-48d0-93db-d093957675c1</t>
+    <t>aa4a5466-e30a-4c19-ad67-e8ae92b6b08e</t>
   </si>
   <si>
     <t>14.04</t>
@@ -1102,7 +1141,7 @@
     <t>אספקה והתקנת דופן מדורגת Corian Glacier White בעובי 12 מ״מ וברוחב 29 ס״מ, עם פינות מעוגלות, על מסגרת מתכת המתומחרת בנפרד, באזור {זיהוי}. אורך ותוואי {לפי הסניף}.</t>
   </si>
   <si>
-    <t>aa3618dd-746f-4f87-affc-2f103d6e3fe9</t>
+    <t>f9cd6ac3-57a0-4b9e-993f-2981bd6e1200</t>
   </si>
   <si>
     <t>14.05</t>
@@ -1111,16 +1150,16 @@
     <t>אספקה והתקנת דופן מדורגת Corian Glacier White בעובי 12 מ״מ וברוחב 32 ס״מ, עם פינות מעוגלות, על מסגרת מתכת המתומחרת בנפרד, באזור {זיהוי}. אורך ותוואי {לפי הסניף}.</t>
   </si>
   <si>
-    <t>f73fa722-1ea6-4368-ad3b-c095740b75da</t>
+    <t>e4b00908-8e61-4264-a732-2e89bbf1d980</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 14 להעברה</t>
   </si>
   <si>
-    <t>פרק אספקות נפתח רק כשהאספקה נפרדת מהתקנה. מפרטי הגמר שנקבעו בשורות הרשת חלים גם על האספקה המקבילה; אין לבחור חומר אחר בשורת האספקה. דגמי גופי התאורה טרם בוססו כסטנדרט עדכני: BF-08. יש להגדיר לכל טיפוס גוף, מסילה או פרופיל סעיף עצמאי; התקנה והזנה בפרק החשמל. כמויות ופחת ייקבעו בפרויקט.</t>
-  </si>
-  <si>
-    <t>5ea8ad7f-0828-41b3-8b09-d4e8b0f57a07</t>
+    <t>פרק אספקות נפתח רק כשהאספקה נפרדת מהתקנה. מפרטי הגמר שנקבעו בשורות הרשת חלים גם על האספקה המקבילה; אין לבחור חומר אחר בשורת האספקה. דגמי גופי התאורה יוגדרו בפרויקט. יש להגדיר לכל טיפוס גוף, מסילה או פרופיל סעיף עצמאי; התקנה והזנה בפרק החשמל. כמויות ופחת ייקבעו בפרויקט.</t>
+  </si>
+  <si>
+    <t>84a29566-fecf-4999-a1bf-7126403cd4c5</t>
   </si>
   <si>
     <t>15.01</t>
@@ -1129,7 +1168,7 @@
     <t>אספקת אריחי ריצוף או חיפוי מטיפוס {זיהוי}, מחומר ודגם {מפרט}, במידה ובגמר {מפרט}. הובלה ופריקה: {תכולה}; התקנה מתומחרת בנפרד.</t>
   </si>
   <si>
-    <t>400177af-7fe0-43eb-a111-588c4f445c3c</t>
+    <t>f73dcd64-b7cf-4ce3-8317-d27edadabfd7</t>
   </si>
   <si>
     <t>15.02</t>
@@ -1138,7 +1177,7 @@
     <t>אספקת כלי או אביזר סניטרי מטיפוס {זיהוי}, בדגם ובגמר {מפרט}, לרבות {אביזרים נלווים}. התקנה וחיבור מתומחרים בפרק האינסטלציה.</t>
   </si>
   <si>
-    <t>46d13d85-a281-4238-ada6-b1d8c670556c</t>
+    <t>0d45b081-ec8d-4133-8046-5af0036aa59e</t>
   </si>
   <si>
     <t>15.03</t>
@@ -1147,7 +1186,7 @@
     <t>אספקת גוף תאורה מטיפוס {זיהוי}, במפרט ובדגם {מפרט}, עם {ספק, דרייבר ואביזרים נלווים לפי הנדרש}. התקנה ונקודת הזנה מתומחרות בפרק החשמל.</t>
   </si>
   <si>
-    <t>50741612-b365-4216-8cd4-e3c8884dd716</t>
+    <t>efd28857-305b-4fd6-85d8-ec6e84bf808c</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 15 להעברה</t>
@@ -1156,7 +1195,7 @@
     <t>תוכן מערכת זו יושלם בפרויקט לפי תכנון היועץ ורשימת הציוד המאושרים. שורות התבנית מגדירות גבולות תכולה ואינן מפרט הנדסי מלא. אין להסיק מהפעלת הפרק שהמערכת נדרשת בכל אתר.</t>
   </si>
   <si>
-    <t>e89605ed-c940-4327-bd98-9501b7725240</t>
+    <t>ef7704e1-ed59-4f8d-9ae1-16b09bf78631</t>
   </si>
   <si>
     <t>16.01</t>
@@ -1165,13 +1204,13 @@
     <t>ביצוע מערכת מיזוג ואוורור בתכולת {מערכת מוגדרת}, לפי תכנון {הפניה}, לרבות {אספקה, התקנה, חיבור והפעלה}. גבולות מול חשמל, ניקוז ותקרות: {פירוט}.</t>
   </si>
   <si>
-    <t>eb037280-056d-42ef-a362-1f0023849d3e</t>
+    <t>257e110a-1fbc-4db6-93f0-5515f5fb40ac</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 16 להעברה</t>
   </si>
   <si>
-    <t>8b3c1c07-f9b4-4244-ac0a-e02bcb47a252</t>
+    <t>68474170-171e-4b5f-8c83-12ec210918be</t>
   </si>
   <si>
     <t>17.01</t>
@@ -1180,7 +1219,7 @@
     <t>אספקה והתקנת פריט ציוד מטבח או נירוסטה {זיהוי}, לפי רשימת ציוד {הפניה}, בתכולת {מפרט}, עם גבולות חיבור למערכות {פירוט}.</t>
   </si>
   <si>
-    <t>43ed42ac-04e6-42ed-bcfb-ba2ea0937ba3</t>
+    <t>0e495b05-032e-4bca-977e-fa8fb74fe5d4</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 17 להעברה</t>
@@ -1189,7 +1228,7 @@
     <t>מערכת הגז נפתחת רק כשנדרשת בתכנון הפרויקט. תשתית, אביזרים, בדיקות וגבולות חיבור ייקבעו במפרט המתכנן והגורם המבצע; אין הנחת סוג צנרת, צובר קיים או מיקום ציוד מהארכיון.</t>
   </si>
   <si>
-    <t>bd0cb7cf-2954-4926-8dd0-9e6dd447fb29</t>
+    <t>564ed72b-b477-49ae-b76a-3d2ab5552342</t>
   </si>
   <si>
     <t>18.01</t>
@@ -1198,13 +1237,13 @@
     <t>ביצוע נקודת גז עבור {ציוד מזוהה}, לפי תכנון {הפניה}, לרבות התשתית ואביזרי החיבור בתכולת {מפרט}. גבולות אחריות אספקת המערכת, חיבור הציוד ובדיקות: {פירוט}.</t>
   </si>
   <si>
-    <t>11c1874d-e02a-4d99-bae8-6e1f6ed480bb</t>
+    <t>98676dda-475c-4597-bcca-67632b6a3820</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 18 להעברה</t>
   </si>
   <si>
-    <t>081bd666-a85d-432b-a361-7d4d2a7a0724</t>
+    <t>b03f66d9-6f82-49d5-a5c6-86af33545730</t>
   </si>
   <si>
     <t>19.01</t>
@@ -1213,7 +1252,7 @@
     <t>ביצוע מערכת כיבוי {סוג מערכת מוגדר}, לפי תכנון בטיחות וכיבוי {הפניה}, בגבולות {תכולה ואחריות}, עם הממשקים למערכות האחרות כמפורט.</t>
   </si>
   <si>
-    <t>7582ad5a-817c-4a6e-89fa-aed0e5d540f5</t>
+    <t>c4ff5f50-43e2-4dc3-a3ab-b498da0e39f2</t>
   </si>
   <si>
     <t>19.02</t>
@@ -1222,13 +1261,13 @@
     <t>ביצוע מערכת גילוי או התרעה {סוג מערכת מוגדר}, לפי תכנון {הפניה}, בגבולות {תכולה ואחריות}, עם ההכנות והחיבורים המפורטים.</t>
   </si>
   <si>
-    <t>2c1bc97f-7c6f-4322-bd74-8d582df9ab9d</t>
+    <t>5e219e32-96a7-40bb-bd6c-8c236879e2bf</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 19 להעברה</t>
   </si>
   <si>
-    <t>85d398ac-d801-45b6-ad38-25eaa60363a8</t>
+    <t>97e9a465-1bb8-4b58-844b-eff4f5563b6e</t>
   </si>
   <si>
     <t>20.01</t>
@@ -1237,7 +1276,7 @@
     <t>אספקה והתקנת שילוט או אותיות מטיפוס {זיהוי}, במידות ובחומר {מפרט}, בגמר {גמר}, לרבות {תאורה, ספק, פרזול והתקנה}. תשתית והזנה מתומחרות בנפרד אם צוינו בפרק החשמל.</t>
   </si>
   <si>
-    <t>b419cbf9-e1c1-4cbb-b922-551bda1c93e2</t>
+    <t>6a7e008e-3054-4c0d-bb84-aed47eb43152</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 20 להעברה</t>
@@ -1246,7 +1285,7 @@
     <t>מחיר כל פריט נגרות כולל את החומרים, החיפויים, הפרזול, הגמר, ההובלה וההרכבה שפורטו בסעיף. רכיבי מתכת, משטחי אבן או חומר מיוחד, זיגוג וציוד שמופיעים בפרק נפרד מוחרגים ממחיר הנגרות. מידות, גוונים ודגמים יושלמו לכל פריט.</t>
   </si>
   <si>
-    <t>9d72ad11-d181-4a95-8f42-8f46cb7a5c8d</t>
+    <t>11159066-0048-42c5-86f0-f4b07057a7b0</t>
   </si>
   <si>
     <t>21.01</t>
@@ -1255,7 +1294,7 @@
     <t>אספקת פריט ריהוט נייד מטיפוס {זיהוי}, בדגם ובגמר {מפרט}, לרבות {הובלה והרכבה}.</t>
   </si>
   <si>
-    <t>efa2d487-7bff-4c57-9999-f2892375b0fe</t>
+    <t>8cdb6242-f61d-4a8f-b38c-976d57a1c761</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 21 להעברה</t>
@@ -1277,12 +1316,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;תאריך: &quot;@"/>
     <numFmt numFmtId="165" formatCode="&quot;פרק &quot;0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    <numFmt numFmtId="167" formatCode="[=0]#,##0&quot;₪&quot;;#,##0.00&quot;₪&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;₪&quot;"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1496,7 +1533,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1522,10 +1559,10 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
@@ -1534,1214 +1571,31 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="394">
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3301,14 +2155,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -3316,13 +2170,13 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -3331,7 +2185,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -3364,7 +2218,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -3383,30 +2237,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="136" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="138" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="140" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -3416,7 +2246,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="10" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="11" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -3428,7 +2258,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.29" customWidth="1"/>
@@ -3484,25 +2314,25 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="99" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>114</v>
@@ -3514,7 +2344,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -3522,10 +2352,10 @@
     </row>
     <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>114</v>
@@ -3537,7 +2367,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -3545,10 +2375,10 @@
     </row>
     <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>114</v>
@@ -3560,7 +2390,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -3568,10 +2398,10 @@
     </row>
     <row r="7" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>134</v>
@@ -3583,7 +2413,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -3591,10 +2421,10 @@
     </row>
     <row r="8" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>114</v>
@@ -3606,7 +2436,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -3614,10 +2444,10 @@
     </row>
     <row r="9" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>114</v>
@@ -3629,153 +2459,78 @@
         <v/>
       </c>
       <c r="G9" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" ht="139.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="21"/>
+    <row r="10" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="4"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23" t="str">
+        <f>IF(ISBLANK(D10),"",IF(NOT(ISNUMBER(D10)),"קלט לא תקין",IF(D10&lt;0,"קלט לא תקין",IF(ISBLANK(E10),"",IF(OR(E10="כלול",E10="לא רלוונטי"),0,IF(NOT(ISNUMBER(E10)),"קלט לא תקין",IF(E10&lt;0,"קלט לא תקין",ROUND(D10*E10,2))))))))</f>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>256</v>
+      </c>
       <c r="H10" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="24">
-        <f>SUM(F4,F5,F6,F7,F8,F9)</f>
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" ht="93" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="24">
+        <f>SUM(F4,F5,F6,F7,F8,F9,F10)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="142" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="144" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="145" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="146" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="148" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="149" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="150" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="151" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="152" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="154" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="155" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="156" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="158" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="159" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="160" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="162" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="164" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="166" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D9">
+  <dataValidations count="9">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D10">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E10">
+      <formula1>OR(ISBLANK(E10),AND(ISNUMBER(E10),E10&gt;=0),E10="כלול",E10="לא רלוונטי")</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E4">
       <formula1>OR(ISBLANK(E4),AND(ISNUMBER(E4),E4&gt;=0),E4="כלול",E4="לא רלוונטי")</formula1>
@@ -3797,7 +2552,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="11" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="12" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -3865,28 +2620,28 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -3895,21 +2650,21 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
@@ -3918,25 +2673,36 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" ht="400" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="21"/>
+    <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="4"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23" t="str">
+        <f>IF(ISBLANK(D6),"",IF(NOT(ISNUMBER(D6)),"קלט לא תקין",IF(D6&lt;0,"קלט לא תקין",IF(ISBLANK(E6),"",IF(OR(E6="כלול",E6="לא רלוונטי"),0,IF(NOT(ISNUMBER(E6)),"קלט לא תקין",IF(E6&lt;0,"קלט לא תקין",ROUND(D6*E6,2))))))))</f>
+        <v/>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>268</v>
+      </c>
       <c r="H6" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="48.80000000000001" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" ht="367.20000000000005" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21"/>
       <c r="B7" s="22"/>
       <c r="C7" s="21"/>
@@ -3951,13 +2717,13 @@
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="24">
-        <f>SUM(F4,F5)</f>
+        <f>SUM(F4,F5,F6)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4"/>
@@ -3970,48 +2736,8 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="168" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="170" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="171" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="172" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="174" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="175" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="176" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D5">
+  <dataValidations count="4">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E4">
@@ -4020,9 +2746,12 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E5">
       <formula1>OR(ISBLANK(E5),AND(ISNUMBER(E5),E5&gt;=0),E5="כלול",E5="לא רלוונטי")</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E6">
+      <formula1>OR(ISBLANK(E6),AND(ISNUMBER(E6),E6&gt;=0),E6="כלול",E6="לא רלוונטי")</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="12" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="13" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -4090,14 +2819,14 @@
     <row r="3" ht="116.39999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -4105,10 +2834,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>114</v>
@@ -4120,7 +2849,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -4128,10 +2857,10 @@
     </row>
     <row r="5" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>114</v>
@@ -4143,7 +2872,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -4151,10 +2880,10 @@
     </row>
     <row r="6" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>114</v>
@@ -4166,7 +2895,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -4187,7 +2916,7 @@
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -4206,62 +2935,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="178" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="179" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="180" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="182" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="183" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="184" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="185" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="186" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="188" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="189" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="190" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="191" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
@@ -4277,7 +2950,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="13" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="14" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -4342,17 +3015,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" ht="116.39999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" ht="99" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -4360,10 +3033,10 @@
     </row>
     <row r="4" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>134</v>
@@ -4375,7 +3048,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -4383,10 +3056,10 @@
     </row>
     <row r="5" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>134</v>
@@ -4398,18 +3071,18 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>134</v>
@@ -4421,7 +3094,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -4429,13 +3102,13 @@
     </row>
     <row r="7" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -4444,7 +3117,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -4452,10 +3125,10 @@
     </row>
     <row r="8" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>114</v>
@@ -4467,7 +3140,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -4475,10 +3148,10 @@
     </row>
     <row r="9" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>114</v>
@@ -4490,13 +3163,13 @@
         <v/>
       </c>
       <c r="G9" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" ht="35.39999999999998" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" ht="70.20000000000005" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="22"/>
       <c r="C10" s="21"/>
@@ -4511,7 +3184,7 @@
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -4530,110 +3203,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B11:E11"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="192" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="193" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="194" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="196" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="197" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="198" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="199" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="200" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="201" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="202" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="203" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="204" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="206" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="207" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="208" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="209" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="210" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="211" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="212" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="213" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="214" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="215" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="216" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="217" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D9">
       <formula1>0</formula1>
@@ -4658,7 +3227,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="14" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="15" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -4726,14 +3295,14 @@
     <row r="3" ht="116.39999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -4741,10 +3310,10 @@
     </row>
     <row r="4" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>134</v>
@@ -4756,7 +3325,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -4764,13 +3333,13 @@
     </row>
     <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
@@ -4779,7 +3348,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -4787,13 +3356,13 @@
     </row>
     <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -4802,7 +3371,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -4810,10 +3379,10 @@
     </row>
     <row r="7" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>134</v>
@@ -4825,7 +3394,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -4833,10 +3402,10 @@
     </row>
     <row r="8" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>134</v>
@@ -4848,7 +3417,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -4856,13 +3425,13 @@
     </row>
     <row r="9" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
@@ -4871,7 +3440,7 @@
         <v/>
       </c>
       <c r="G9" s="4" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>108</v>
@@ -4879,13 +3448,13 @@
     </row>
     <row r="10" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
@@ -4894,7 +3463,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>108</v>
@@ -4917,7 +3486,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -4925,7 +3494,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>313</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4954,10 +3523,10 @@
     </row>
     <row r="14" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>134</v>
@@ -4969,7 +3538,7 @@
         <v/>
       </c>
       <c r="G14" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>108</v>
@@ -5002,7 +3571,7 @@
     <row r="17" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -5022,142 +3591,6 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B17:E17"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="218" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="219" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="220" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="221" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="222" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="223" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="224" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="225" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="226" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="227" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="228" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="229" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="230" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="231" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="232" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="233" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="234" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="235" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="236" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="237" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="238" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="239" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="240" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="241" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="242" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="243" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="244" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="245" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="expression" dxfId="246" priority="1">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)=INT(ROUND(E14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="247" priority="2">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)&lt;&gt;INT(ROUND(E14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="248" priority="1">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)=INT(ROUND(F14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="249" priority="2">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)&lt;&gt;INT(ROUND(F14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="250" priority="1">
-      <formula>AND(ISNUMBER(F17),ROUND(F17,2)=INT(ROUND(F17,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="251" priority="2">
-      <formula>AND(ISNUMBER(F17),ROUND(F17,2)&lt;&gt;INT(ROUND(F17,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10">
       <formula1>0</formula1>
@@ -5194,7 +3627,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="15" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="16" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -5265,14 +3698,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -5280,10 +3713,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>134</v>
@@ -5295,7 +3728,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -5303,10 +3736,10 @@
     </row>
     <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>134</v>
@@ -5318,7 +3751,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -5326,13 +3759,13 @@
     </row>
     <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -5341,7 +3774,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -5349,10 +3782,10 @@
     </row>
     <row r="7" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>134</v>
@@ -5364,7 +3797,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -5385,7 +3818,7 @@
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -5404,78 +3837,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B9:E9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="252" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="253" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="254" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="255" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="256" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="257" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="258" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="259" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="260" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="261" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="262" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="263" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="264" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="265" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="266" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="267" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="268" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="269" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D7">
       <formula1>0</formula1>
@@ -5494,7 +3855,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="17" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="18" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -5562,14 +3923,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -5577,10 +3938,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>134</v>
@@ -5592,7 +3953,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -5600,10 +3961,10 @@
     </row>
     <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>134</v>
@@ -5615,7 +3976,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -5623,10 +3984,10 @@
     </row>
     <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>134</v>
@@ -5638,7 +3999,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -5646,10 +4007,10 @@
     </row>
     <row r="7" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>134</v>
@@ -5661,7 +4022,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -5669,10 +4030,10 @@
     </row>
     <row r="8" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>134</v>
@@ -5684,7 +4045,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -5705,7 +4066,7 @@
     <row r="10" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="15" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -5724,94 +4085,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="270" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="271" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="272" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="273" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="274" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="275" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="276" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="277" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="278" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="279" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="280" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="281" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="282" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="283" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="284" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="285" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="286" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="287" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="288" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="289" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="290" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="291" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D8">
       <formula1>0</formula1>
@@ -5833,7 +4106,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="18" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="19" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -5901,14 +4174,14 @@
     <row r="3" ht="99" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -5916,10 +4189,10 @@
     </row>
     <row r="4" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>114</v>
@@ -5931,7 +4204,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -5939,13 +4212,13 @@
     </row>
     <row r="5" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
@@ -5954,7 +4227,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -5962,13 +4235,13 @@
     </row>
     <row r="6" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -5977,7 +4250,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -5998,7 +4271,7 @@
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -6017,62 +4290,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="292" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="293" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="294" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="295" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="296" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="297" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="298" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="299" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="300" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="301" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="302" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="303" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="304" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="305" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
@@ -6088,7 +4305,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="19" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="20" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -6156,14 +4373,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -6171,10 +4388,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>106</v>
@@ -6186,7 +4403,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -6219,7 +4436,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -6238,30 +4455,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="306" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="307" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="308" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="309" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="310" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="311" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -6271,7 +4464,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="20" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="21" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -6385,7 +4578,7 @@
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6399,7 +4592,7 @@
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6413,7 +4606,7 @@
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6427,7 +4620,7 @@
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,7 +4634,7 @@
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,7 +4648,7 @@
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
       <c r="F12" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6469,7 +4662,7 @@
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6483,7 +4676,7 @@
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6497,7 +4690,7 @@
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,7 +4704,7 @@
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6525,7 +4718,7 @@
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,7 +4732,7 @@
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,7 +4746,7 @@
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6567,7 +4760,7 @@
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6581,7 +4774,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,7 +4788,7 @@
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6645,7 +4838,7 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6850,14 +5043,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -6865,13 +5058,13 @@
     </row>
     <row r="4" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -6880,7 +5073,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -6913,7 +5106,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -6932,30 +5125,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="312" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="313" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="314" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="315" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="316" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="317" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -6965,7 +5134,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="21" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="22" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -7033,14 +5202,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -7048,13 +5217,13 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -7063,7 +5232,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -7096,7 +5265,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7115,30 +5284,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="318" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="319" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="320" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="321" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="322" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="323" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -7148,7 +5293,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="22" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="23" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -7216,14 +5361,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -7231,10 +5376,10 @@
     </row>
     <row r="4" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>106</v>
@@ -7246,7 +5391,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -7254,10 +5399,10 @@
     </row>
     <row r="5" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>106</v>
@@ -7269,7 +5414,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -7302,7 +5447,7 @@
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -7321,46 +5466,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="324" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="325" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="326" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="327" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="328" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="329" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="330" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="331" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="332" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="333" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D5">
       <formula1>0</formula1>
@@ -7373,7 +5478,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="23" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="24" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -7441,14 +5546,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -7456,13 +5561,13 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -7471,7 +5576,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -7504,7 +5609,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7523,30 +5628,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="334" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="335" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="336" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="337" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="338" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="339" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -7556,7 +5637,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="24" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="25" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -7624,14 +5705,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -7639,13 +5720,13 @@
     </row>
     <row r="4" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -7654,7 +5735,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -7687,7 +5768,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7706,30 +5787,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="340" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="341" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="342" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="343" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="344" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="345" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -7739,7 +5796,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="25" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="26" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -7765,7 +5822,7 @@
     <row r="1" ht="40" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="12" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -7777,7 +5834,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -7811,7 +5868,7 @@
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
       <c r="E4" s="34">
-        <f>'מחיצות והכנות לדלפק'!F10</f>
+        <f>'מחיצות והכנות לדלפק'!F11</f>
         <v>0</v>
       </c>
       <c r="F4" s="35"/>
@@ -7841,7 +5898,7 @@
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
       <c r="E6" s="34">
-        <f>'חשמל והכנות תקשורת'!F15</f>
+        <f>'חשמל והכנות תקשורת'!F20</f>
         <v>0</v>
       </c>
       <c r="F6" s="35"/>
@@ -7901,7 +5958,7 @@
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="E10" s="34">
-        <f>'ריצוף וחיפוי הדלפק'!F11</f>
+        <f>'ריצוף וחיפוי הדלפק'!F12</f>
         <v>0</v>
       </c>
       <c r="F10" s="35"/>
@@ -8104,7 +6161,7 @@
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="36" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="37"/>
@@ -8141,7 +6198,7 @@
     <row r="27" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="46" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -8206,200 +6263,8 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="E27:F27"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="expression" dxfId="346" priority="1">
-      <formula>AND(ISNUMBER(E3),ROUND(E3,2)=INT(ROUND(E3,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="347" priority="2">
-      <formula>AND(ISNUMBER(E3),ROUND(E3,2)&lt;&gt;INT(ROUND(E3,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="348" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="349" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="350" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="351" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="352" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="353" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="354" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="355" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="356" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="357" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="358" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="359" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="360" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="361" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="362" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="363" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="expression" dxfId="364" priority="1">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)=INT(ROUND(E12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="365" priority="2">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)&lt;&gt;INT(ROUND(E12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="366" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="367" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="expression" dxfId="368" priority="1">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)=INT(ROUND(E14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="369" priority="2">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)&lt;&gt;INT(ROUND(E14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="expression" dxfId="370" priority="1">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)=INT(ROUND(E15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="371" priority="2">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)&lt;&gt;INT(ROUND(E15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="expression" dxfId="372" priority="1">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)=INT(ROUND(E16,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="373" priority="2">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)&lt;&gt;INT(ROUND(E16,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="374" priority="1">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)=INT(ROUND(E17,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="375" priority="2">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)&lt;&gt;INT(ROUND(E17,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="expression" dxfId="376" priority="1">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)=INT(ROUND(E18,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="377" priority="2">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)&lt;&gt;INT(ROUND(E18,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="expression" dxfId="378" priority="1">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)=INT(ROUND(E19,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="379" priority="2">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)&lt;&gt;INT(ROUND(E19,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
-    <cfRule type="expression" dxfId="380" priority="1">
-      <formula>AND(ISNUMBER(E20),ROUND(E20,2)=INT(ROUND(E20,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="381" priority="2">
-      <formula>AND(ISNUMBER(E20),ROUND(E20,2)&lt;&gt;INT(ROUND(E20,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="expression" dxfId="382" priority="1">
-      <formula>AND(ISNUMBER(E21),ROUND(E21,2)=INT(ROUND(E21,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="383" priority="2">
-      <formula>AND(ISNUMBER(E21),ROUND(E21,2)&lt;&gt;INT(ROUND(E21,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
-    <cfRule type="expression" dxfId="384" priority="1">
-      <formula>AND(ISNUMBER(E22),ROUND(E22,2)=INT(ROUND(E22,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="385" priority="2">
-      <formula>AND(ISNUMBER(E22),ROUND(E22,2)&lt;&gt;INT(ROUND(E22,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23">
-    <cfRule type="expression" dxfId="386" priority="1">
-      <formula>AND(ISNUMBER(E23),ROUND(E23,2)=INT(ROUND(E23,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="387" priority="2">
-      <formula>AND(ISNUMBER(E23),ROUND(E23,2)&lt;&gt;INT(ROUND(E23,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
-    <cfRule type="expression" dxfId="388" priority="1">
-      <formula>AND(ISNUMBER(E25),ROUND(E25,2)=INT(ROUND(E25,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="389" priority="2">
-      <formula>AND(ISNUMBER(E25),ROUND(E25,2)&lt;&gt;INT(ROUND(E25,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
-    <cfRule type="expression" dxfId="390" priority="1">
-      <formula>AND(ISNUMBER(E26),ROUND(E26,2)=INT(ROUND(E26,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="391" priority="2">
-      <formula>AND(ISNUMBER(E26),ROUND(E26,2)&lt;&gt;INT(ROUND(E26,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="expression" dxfId="392" priority="1">
-      <formula>AND(ISNUMBER(E27),ROUND(E27,2)=INT(ROUND(E27,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="393" priority="2">
-      <formula>AND(ISNUMBER(E27),ROUND(E27,2)&lt;&gt;INT(ROUND(E27,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="26" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="27" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -9031,126 +6896,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="10" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="14" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="16" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="20" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="22" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="24" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="26" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="expression" dxfId="28" priority="1">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)=INT(ROUND(F12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="2">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)&lt;&gt;INT(ROUND(F12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10">
       <formula1>0</formula1>
@@ -9193,7 +6938,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.29" customWidth="1"/>
@@ -9285,7 +7030,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>136</v>
       </c>
@@ -9316,7 +7061,7 @@
         <v>140</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -9325,7 +7070,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -9333,13 +7078,13 @@
     </row>
     <row r="7" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>144</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>141</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -9362,7 +7107,7 @@
         <v>147</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -9377,130 +7122,65 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" ht="308.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="21"/>
+    <row r="9" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>144</v>
+      </c>
       <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="4"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23" t="str">
+        <f>IF(ISBLANK(D9),"",IF(NOT(ISNUMBER(D9)),"קלט לא תקין",IF(D9&lt;0,"קלט לא תקין",IF(ISBLANK(E9),"",IF(OR(E9="כלול",E9="לא רלוונטי"),0,IF(NOT(ISNUMBER(E9)),"קלט לא תקין",IF(E9&lt;0,"קלט לא תקין",ROUND(D9*E9,2))))))))</f>
+        <v/>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="H9" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="24">
-        <f>SUM(F4,F5,F6,F7,F8)</f>
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" ht="226.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="24">
+        <f>SUM(F4,F5,F6,F7,F8,F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="30" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="32" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="34" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="36" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="38" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="40" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="42" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="44" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="46" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="48" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="50" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D8">
+  <dataValidations count="7">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D9">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E4">
@@ -9517,6 +7197,9 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E8">
       <formula1>OR(ISBLANK(E8),AND(ISNUMBER(E8),E8&gt;=0),E8="כלול",E8="לא רלוונטי")</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E9">
+      <formula1>OR(ISBLANK(E9),AND(ISNUMBER(E9),E9&gt;=0),E9="כלול",E9="לא רלוונטי")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
@@ -9588,14 +7271,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -9603,10 +7286,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>106</v>
@@ -9618,7 +7301,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -9626,13 +7309,13 @@
     </row>
     <row r="5" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
@@ -9641,7 +7324,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -9649,13 +7332,13 @@
     </row>
     <row r="6" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>160</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>157</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -9664,7 +7347,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -9672,13 +7355,13 @@
     </row>
     <row r="7" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -9687,7 +7370,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -9695,13 +7378,13 @@
     </row>
     <row r="8" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -9710,7 +7393,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -9718,13 +7401,13 @@
     </row>
     <row r="9" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
@@ -9733,7 +7416,7 @@
         <v/>
       </c>
       <c r="G9" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>108</v>
@@ -9741,13 +7424,13 @@
     </row>
     <row r="10" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
@@ -9756,7 +7439,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>108</v>
@@ -9777,7 +7460,7 @@
     <row r="12" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -9796,126 +7479,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="52" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="54" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="56" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="58" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="60" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="62" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="64" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="66" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="68" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="70" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="72" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="74" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="76" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="78" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="expression" dxfId="80" priority="1">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)=INT(ROUND(F12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="2">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)&lt;&gt;INT(ROUND(F12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10">
       <formula1>0</formula1>
@@ -9958,7 +7521,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.29" customWidth="1"/>
@@ -10014,14 +7577,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -10029,13 +7592,13 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -10044,7 +7607,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -10052,13 +7615,13 @@
     </row>
     <row r="5" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
@@ -10067,7 +7630,7 @@
         <v/>
       </c>
       <c r="G5" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>108</v>
@@ -10075,13 +7638,13 @@
     </row>
     <row r="6" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="23"/>
@@ -10090,7 +7653,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>108</v>
@@ -10098,13 +7661,13 @@
     </row>
     <row r="7" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -10113,7 +7676,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
@@ -10121,13 +7684,13 @@
     </row>
     <row r="8" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -10136,7 +7699,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>108</v>
@@ -10144,13 +7707,13 @@
     </row>
     <row r="9" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
@@ -10159,7 +7722,7 @@
         <v/>
       </c>
       <c r="G9" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>108</v>
@@ -10167,13 +7730,13 @@
     </row>
     <row r="10" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
@@ -10182,7 +7745,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>108</v>
@@ -10190,13 +7753,13 @@
     </row>
     <row r="11" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="23"/>
@@ -10205,7 +7768,7 @@
         <v/>
       </c>
       <c r="G11" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>108</v>
@@ -10213,10 +7776,10 @@
     </row>
     <row r="12" ht="46.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>106</v>
@@ -10228,7 +7791,7 @@
         <v/>
       </c>
       <c r="G12" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>108</v>
@@ -10236,13 +7799,13 @@
     </row>
     <row r="13" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="23"/>
@@ -10251,218 +7814,141 @@
         <v/>
       </c>
       <c r="G13" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" ht="22.200000000000045" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+    <row r="14" ht="54.200000000000045" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="24">
-        <f>SUM(F4,F5,F6,F7,F8,F9,F10,F11,F12,F13)</f>
-        <v>0</v>
-      </c>
+      <c r="A15" s="27">
+        <v>4</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23" t="str">
+        <f>IF(ISBLANK(D17),"",IF(NOT(ISNUMBER(D17)),"קלט לא תקין",IF(D17&lt;0,"קלט לא תקין",IF(ISBLANK(E17),"",IF(OR(E17="כלול",E17="לא רלוונטי"),0,IF(NOT(ISNUMBER(E17)),"קלט לא תקין",IF(E17&lt;0,"קלט לא תקין",ROUND(D17*E17,2))))))))</f>
+        <v/>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" ht="400" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="142.39999999999998" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="24">
+        <f>SUM(F4,F5,F6,F7,F8,F9,F10,F11,F12,F13,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:E20"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="82" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="84" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="86" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="88" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="90" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="92" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="94" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="96" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="98" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="100" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="102" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="104" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="106" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="108" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="110" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="112" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="expression" dxfId="114" priority="1">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)=INT(ROUND(E12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="2">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)&lt;&gt;INT(ROUND(E12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="expression" dxfId="116" priority="1">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)=INT(ROUND(F12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="2">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)&lt;&gt;INT(ROUND(F12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="118" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="120" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="122" priority="1">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)=INT(ROUND(F15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="2">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)&lt;&gt;INT(ROUND(F15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="14">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10:D13">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D17">
+      <formula1>0</formula1>
+    </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D13">
       <formula1>0</formula1>
     </dataValidation>
@@ -10477,6 +7963,9 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E13">
       <formula1>OR(ISBLANK(E13),AND(ISNUMBER(E13),E13&gt;=0),E13="כלול",E13="לא רלוונטי")</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E17">
+      <formula1>OR(ISBLANK(E17),AND(ISNUMBER(E17),E17&gt;=0),E17="כלול",E17="לא רלוונטי")</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="מספר לא שלילי, כלול או לא רלוונטי בלבד" sqref="E4">
       <formula1>OR(ISBLANK(E4),AND(ISNUMBER(E4),E4&gt;=0),E4="כלול",E4="לא רלוונטי")</formula1>
@@ -10502,6 +7991,9 @@
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16838" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -10566,14 +8058,14 @@
     <row r="3" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -10581,10 +8073,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>114</v>
@@ -10596,7 +8088,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -10629,7 +8121,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -10648,30 +8140,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="124" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="126" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="127" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="128" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -10681,7 +8149,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="8" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="9" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
@@ -10749,14 +8217,14 @@
     <row r="3" ht="81.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="22" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
       <c r="G3" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>103</v>
@@ -10764,10 +8232,10 @@
     </row>
     <row r="4" ht="64.19999999999999" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>114</v>
@@ -10779,7 +8247,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>108</v>
@@ -10812,7 +8280,7 @@
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -10831,30 +8299,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="130" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="132" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="134" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -10864,7 +8308,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="9" useFirstPageNumber="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="10" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;Cעמוד &amp;P</oddFooter>
   </headerFooter>
